--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -498,7 +498,7 @@
 </t>
   </si>
   <si>
-    <t>機械判定</t>
+    <t>機械判定された所見・解釈の有無</t>
   </si>
   <si>
     <t>心電図検査の所見が機械的に判定されたものであるかどうかを示す</t>
@@ -1087,7 +1087,7 @@
 CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
   </si>
   <si>
-    <t>心電図の測定結果</t>
+    <t>心電図の測定結果。心電図の測定値は単一の値では示されないため通常は用いられない。</t>
   </si>
   <si>
     <t>心電図検査は一つの測定値のみを用いられることはなく、一連の測定値を元にして所見を得て解釈される。単一の測定値としてのこの項目は空欄であることが前提であるが、送受信側の双方が合意して単一の測定値のみを送信するためにこのリソースを仕様することも許容される。</t>
@@ -1580,7 +1580,7 @@
     <t>高、低、正常など。 / High, low, normal, etc.</t>
   </si>
   <si>
-    <t>観測値のカテゴリー評価。たとえば、高、低、正常。 / A categorical assessment of an observation value.  For example, high, low, normal.</t>
+    <t>心電図検査で測定された結果値に対する所見・解釈</t>
   </si>
   <si>
     <t>心電図検査の測定結果と解釈は必ずしも1対1で対応しないが、PR間隔の測定値にPR間隔延長などの固有の所見をつけてもよい</t>
@@ -6480,7 +6480,7 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>192</v>
+        <v>356</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
@@ -9126,7 +9126,7 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>192</v>
+        <v>356</v>
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="508">
   <si>
     <t>Property</t>
   </si>
@@ -481,7 +481,7 @@
     <t>誘導の数</t>
   </si>
   <si>
-    <t>心電図検査で試用した誘導の数を記録するための拡張</t>
+    <t>心電図検査で使用した誘導の数を記録するための拡張</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -1087,10 +1087,10 @@
 CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
   </si>
   <si>
-    <t>心電図の測定結果。心電図の測定値は単一の値では示されないため通常は用いられない。</t>
-  </si>
-  <si>
-    <t>心電図検査は一つの測定値のみを用いられることはなく、一連の測定値を元にして所見を得て解釈される。単一の測定値としてのこの項目は空欄であることが前提であるが、送受信側の双方が合意して単一の測定値のみを送信するためにこのリソースを仕様することも許容される。</t>
+    <t>心電図の測定結果</t>
+  </si>
+  <si>
+    <t>心電図検査は一つの測定値のみを用いられることはなく、一連の測定値を元にして所見を得て総合的に解釈される。単一の測定値としてのこの項目は空欄であることが前提であるが、送受信側の双方が合意して単一の測定値のみを送信するためにこのリソースを仕様することも許容される。</t>
   </si>
   <si>
     <t>観測は値を持つように存在しますが、それが誤っている場合、または観測のグループを表す場合はそうではありません。 / An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
@@ -1150,7 +1150,7 @@
     <t>心電図所見</t>
   </si>
   <si>
-    <t>心電図所見については、ミネソタコードを元に学会や検査機器ベンダーが用語集を作成している。必要に応じてそれらのコードを仕様することを推奨する。</t>
+    <t>心電図所見・解釈について記載する。心電図所見は測定された結果と1対1で対応するものではなく、総合的に判断されるものである。したがって所見や解釈はこのエレメントに列記することとした。所見については、ミネソタコードを元に学会や検査機器ベンダーが用語集を作成している。必要に応じてそれらのコードを仕様することを推奨する。</t>
   </si>
   <si>
     <t>心電図所見についてのコード集を別途提示する。</t>
@@ -1539,6 +1539,9 @@
   </si>
   <si>
     <t>心電図の各検査項目についてはLOINCなどの特定の用語集を利用することが推奨される。</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -6480,7 +6483,7 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>356</v>
+        <v>192</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
@@ -9130,7 +9133,7 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>249</v>
+        <v>487</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9166,7 +9169,7 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>218</v>
@@ -9183,10 +9186,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9212,13 +9215,13 @@
         <v>343</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O61" t="s" s="2">
         <v>346</v>
@@ -9270,7 +9273,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9288,7 +9291,7 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>349</v>
@@ -9305,10 +9308,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9334,13 +9337,13 @@
         <v>201</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O62" t="s" s="2">
         <v>355</v>
@@ -9392,7 +9395,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9427,10 +9430,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9456,16 +9459,16 @@
         <v>201</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9512,7 +9515,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9547,10 +9550,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9576,16 +9579,16 @@
         <v>84</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9634,7 +9637,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2488" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="465">
   <si>
     <t>Property</t>
   </si>
@@ -682,13 +682,7 @@
     <t>どのような観察が行われているかを知ることは、観察を理解するために不可欠です。 / Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -762,6 +756,12 @@
     <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://loinc.org"/&gt;
+  &lt;code value="11524-6"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>CodeableConcept.coding</t>
   </si>
   <si>
@@ -769,133 +769,6 @@
   </si>
   <si>
     <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.system</t>
-  </si>
-  <si>
-    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.version</t>
-  </si>
-  <si>
-    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.code</t>
-  </si>
-  <si>
-    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>11524-6</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.display</t>
-  </si>
-  <si>
-    <t>システムによって定義された表現 / Representation defined by the system</t>
-  </si>
-  <si>
-    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1203,6 +1076,9 @@
     <t>観察結果で見つかったコードで暗黙的ではない場合にのみ使用されます。多くのシステムでは、これはインラインコンポーネントの代わりに関連する観察として表される場合があります。
 ユースケースでは、ボディサイトを個別のリソースとして処理する必要がある場合（たとえば、個別に識別および追跡するため）、標準の拡張[BodySite]（Extension-BodySite.html）を使用します。 / Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>example</t>
   </si>
   <si>
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
@@ -1539,9 +1415,6 @@
   </si>
   <si>
     <t>心電図の各検査項目についてはLOINCなどの特定の用語集を利用することが推奨される。</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -1908,7 +1781,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP64"/>
+  <dimension ref="A1:AP57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.79296875" customWidth="true" bestFit="true"/>
@@ -4065,13 +3938,11 @@
         <v>83</v>
       </c>
       <c r="X18" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y18" s="2"/>
+      <c r="Z18" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>83</v>
@@ -4104,30 +3975,30 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AP18" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>221</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4150,13 +4021,13 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4207,7 +4078,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4231,7 +4102,7 @@
         <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4242,10 +4113,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4271,10 +4142,10 @@
         <v>139</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>161</v>
@@ -4318,7 +4189,7 @@
         <v>142</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>83</v>
@@ -4327,7 +4198,7 @@
         <v>143</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4351,7 +4222,7 @@
         <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4362,10 +4233,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4388,26 +4259,26 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>236</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>83</v>
+        <v>237</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>83</v>
@@ -4449,7 +4320,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4470,10 +4341,10 @@
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4484,10 +4355,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4507,19 +4378,23 @@
         <v>83</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
@@ -4567,7 +4442,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4579,7 +4454,7 @@
         <v>83</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>83</v>
@@ -4588,10 +4463,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>83</v>
+        <v>247</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4602,21 +4477,21 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>83</v>
@@ -4625,21 +4500,23 @@
         <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>139</v>
+        <v>250</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
       </c>
@@ -4675,46 +4552,46 @@
         <v>83</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>231</v>
+        <v>83</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>83</v>
+        <v>254</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>83</v>
+        <v>255</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>227</v>
+        <v>256</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>83</v>
+        <v>257</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>83</v>
@@ -4722,10 +4599,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4736,7 +4613,7 @@
         <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>83</v>
@@ -4748,26 +4625,24 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>108</v>
+        <v>259</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>248</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>249</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4809,13 +4684,13 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>83</v>
@@ -4830,13 +4705,13 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>83</v>
+        <v>257</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>83</v>
@@ -4844,14 +4719,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>83</v>
+        <v>264</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4870,18 +4745,20 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
       </c>
@@ -4929,7 +4806,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4944,19 +4821,19 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>83</v>
+        <v>269</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>83</v>
+        <v>272</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>83</v>
@@ -4964,14 +4841,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>83</v>
+        <v>274</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4990,24 +4867,26 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>114</v>
+        <v>275</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>264</v>
+        <v>83</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>83</v>
@@ -5049,7 +4928,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5064,19 +4943,19 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>83</v>
+        <v>279</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>83</v>
+        <v>282</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>83</v>
@@ -5084,10 +4963,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5110,18 +4989,18 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>223</v>
+        <v>284</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>83</v>
       </c>
@@ -5169,7 +5048,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5190,13 +5069,13 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>83</v>
+        <v>289</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>83</v>
@@ -5204,10 +5083,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5218,7 +5097,7 @@
         <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>83</v>
@@ -5230,19 +5109,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5291,13 +5170,13 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>83</v>
@@ -5306,19 +5185,19 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>83</v>
+        <v>298</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5326,10 +5205,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5352,19 +5231,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>223</v>
+        <v>300</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5413,7 +5292,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5422,7 +5301,7 @@
         <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>106</v>
@@ -5431,27 +5310,27 @@
         <v>83</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>83</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5471,22 +5350,22 @@
         <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>293</v>
+        <v>201</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5511,13 +5390,13 @@
         <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>83</v>
+        <v>313</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>83</v>
+        <v>314</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>83</v>
+        <v>315</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>83</v>
@@ -5535,7 +5414,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5544,25 +5423,25 @@
         <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>83</v>
+        <v>316</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>297</v>
+        <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>298</v>
+        <v>137</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>83</v>
@@ -5570,14 +5449,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>83</v>
+        <v>319</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5593,21 +5472,23 @@
         <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>302</v>
+        <v>201</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5631,13 +5512,11 @@
         <v>83</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>83</v>
@@ -5655,7 +5534,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5673,38 +5552,38 @@
         <v>83</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>218</v>
+        <v>325</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>83</v>
@@ -5713,22 +5592,22 @@
         <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5777,13 +5656,13 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>83</v>
@@ -5792,19 +5671,19 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>312</v>
+        <v>83</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>315</v>
+        <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -5812,14 +5691,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5835,23 +5714,21 @@
         <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>318</v>
+        <v>201</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
@@ -5875,13 +5752,13 @@
         <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>83</v>
+        <v>338</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>83</v>
+        <v>339</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>83</v>
+        <v>340</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -5899,7 +5776,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5914,30 +5791,30 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>322</v>
+        <v>83</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>83</v>
+        <v>341</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>325</v>
+        <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>83</v>
+        <v>344</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5957,21 +5834,23 @@
         <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>327</v>
+        <v>201</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
@@ -5995,13 +5874,13 @@
         <v>83</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>83</v>
+        <v>338</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>83</v>
+        <v>349</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>83</v>
+        <v>350</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>83</v>
@@ -6019,7 +5898,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>326</v>
+        <v>345</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6040,13 +5919,13 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>83</v>
@@ -6054,10 +5933,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6068,7 +5947,7 @@
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -6077,23 +5956,21 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>337</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6141,13 +6018,13 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
@@ -6156,30 +6033,30 @@
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>338</v>
+        <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>83</v>
+        <v>357</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>341</v>
+        <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>83</v>
+        <v>360</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6199,23 +6076,21 @@
         <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>343</v>
+        <v>362</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
@@ -6263,7 +6138,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6272,7 +6147,7 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6281,27 +6156,27 @@
         <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>351</v>
+        <v>368</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6312,7 +6187,7 @@
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>83</v>
@@ -6324,19 +6199,19 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>201</v>
+        <v>370</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6361,13 +6236,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>356</v>
+        <v>83</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>357</v>
+        <v>83</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>358</v>
+        <v>83</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6385,19 +6260,19 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>359</v>
+        <v>83</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>106</v>
+        <v>374</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>83</v>
@@ -6406,10 +6281,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>137</v>
+        <v>375</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6420,21 +6295,21 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>362</v>
+        <v>83</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>83</v>
@@ -6446,20 +6321,16 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>363</v>
+        <v>222</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6483,11 +6354,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6505,49 +6378,49 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>361</v>
+        <v>224</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>367</v>
+        <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>368</v>
+        <v>83</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>369</v>
+        <v>225</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>370</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6566,20 +6439,18 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>372</v>
+        <v>139</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>373</v>
+        <v>227</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>373</v>
+        <v>228</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
@@ -6627,7 +6498,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>371</v>
+        <v>230</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6639,7 +6510,7 @@
         <v>83</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>83</v>
@@ -6648,10 +6519,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>376</v>
+        <v>83</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>377</v>
+        <v>225</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6662,44 +6533,46 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6723,13 +6596,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6747,45 +6620,45 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>384</v>
+        <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>385</v>
+        <v>137</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>386</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6808,20 +6681,16 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>201</v>
+        <v>385</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
       </c>
@@ -6845,13 +6714,13 @@
         <v>83</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>392</v>
+        <v>83</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>83</v>
@@ -6869,7 +6738,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6878,7 +6747,7 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>106</v>
@@ -6890,10 +6759,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -6904,10 +6773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6930,17 +6799,15 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -6989,7 +6856,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6998,7 +6865,7 @@
         <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>106</v>
@@ -7007,27 +6874,27 @@
         <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>399</v>
+        <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>402</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7050,18 +6917,20 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>404</v>
+        <v>201</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7085,13 +6954,13 @@
         <v>83</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>83</v>
+        <v>401</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>83</v>
@@ -7109,7 +6978,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7127,27 +6996,27 @@
         <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>409</v>
+        <v>326</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>410</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7170,19 +7039,19 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>412</v>
+        <v>201</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7207,13 +7076,13 @@
         <v>83</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>83</v>
+        <v>338</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>83</v>
+        <v>410</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>83</v>
@@ -7231,7 +7100,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7243,19 +7112,19 @@
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>416</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>417</v>
+        <v>403</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>418</v>
+        <v>326</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7266,10 +7135,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7292,16 +7161,18 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>223</v>
+        <v>412</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>224</v>
+        <v>413</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>225</v>
+        <v>414</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
@@ -7349,7 +7220,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>226</v>
+        <v>411</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7361,7 +7232,7 @@
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>83</v>
@@ -7373,7 +7244,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>227</v>
+        <v>416</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7384,21 +7255,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>83</v>
@@ -7410,17 +7281,15 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>139</v>
+        <v>221</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>229</v>
+        <v>418</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7469,19 +7338,19 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>232</v>
+        <v>417</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>83</v>
@@ -7490,10 +7359,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>83</v>
+        <v>389</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>227</v>
+        <v>420</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7511,7 +7380,7 @@
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>422</v>
+        <v>83</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7524,26 +7393,24 @@
         <v>83</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>139</v>
+        <v>422</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>423</v>
       </c>
       <c r="M47" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="N47" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7591,7 +7458,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7603,7 +7470,7 @@
         <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>83</v>
@@ -7612,10 +7479,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>83</v>
+        <v>425</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>137</v>
+        <v>426</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7626,10 +7493,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7640,7 +7507,7 @@
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7649,18 +7516,20 @@
         <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M48" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="N48" s="2"/>
+      <c r="N48" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7709,16 +7578,16 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>430</v>
+        <v>83</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7730,10 +7599,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7744,10 +7613,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7758,7 +7627,7 @@
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>83</v>
@@ -7767,19 +7636,23 @@
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>427</v>
+        <v>370</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="O49" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7827,16 +7700,16 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>430</v>
+        <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -7848,10 +7721,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7862,10 +7735,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7888,20 +7761,16 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>201</v>
+        <v>221</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>438</v>
+        <v>222</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>83</v>
       </c>
@@ -7925,13 +7794,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>442</v>
+        <v>83</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>443</v>
+        <v>83</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -7949,7 +7818,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>437</v>
+        <v>224</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7961,19 +7830,19 @@
         <v>83</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>444</v>
+        <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>445</v>
+        <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>369</v>
+        <v>225</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -7984,14 +7853,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8010,20 +7879,18 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>447</v>
+        <v>227</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>448</v>
+        <v>228</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>83</v>
       </c>
@@ -8047,13 +7914,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>451</v>
+        <v>83</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>452</v>
+        <v>83</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8071,7 +7938,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>446</v>
+        <v>230</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8083,19 +7950,19 @@
         <v>83</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>444</v>
+        <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>445</v>
+        <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>369</v>
+        <v>225</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8106,43 +7973,45 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>454</v>
+        <v>139</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>455</v>
+        <v>381</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>457</v>
+        <v>162</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8191,19 +8060,19 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>453</v>
+        <v>383</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>83</v>
@@ -8215,7 +8084,7 @@
         <v>83</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>458</v>
+        <v>137</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8226,10 +8095,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8237,7 +8106,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>94</v>
@@ -8249,19 +8118,23 @@
         <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>460</v>
+        <v>442</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8285,13 +8158,11 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8309,10 +8180,10 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>459</v>
+        <v>441</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>94</v>
@@ -8327,16 +8198,16 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>83</v>
+        <v>445</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>431</v>
+        <v>216</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>462</v>
+        <v>217</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>83</v>
+        <v>218</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8344,10 +8215,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8358,7 +8229,7 @@
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8370,18 +8241,20 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>464</v>
+        <v>300</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>465</v>
+        <v>447</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
       </c>
@@ -8429,13 +8302,13 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>83</v>
@@ -8447,27 +8320,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>83</v>
+        <v>450</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>467</v>
+        <v>306</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>468</v>
+        <v>307</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>83</v>
+        <v>308</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8478,7 +8351,7 @@
         <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>83</v>
@@ -8487,21 +8360,23 @@
         <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>470</v>
+        <v>201</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>471</v>
+        <v>452</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>471</v>
+        <v>453</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -8525,13 +8400,13 @@
         <v>83</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>83</v>
+        <v>313</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>83</v>
+        <v>314</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>83</v>
+        <v>315</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>83</v>
@@ -8549,16 +8424,16 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>469</v>
+        <v>451</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>83</v>
+        <v>316</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>106</v>
@@ -8570,10 +8445,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>467</v>
+        <v>137</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>473</v>
+        <v>317</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8584,14 +8459,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>474</v>
+        <v>455</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>474</v>
+        <v>455</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>83</v>
+        <v>319</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8607,22 +8482,22 @@
         <v>83</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>412</v>
+        <v>201</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>476</v>
+        <v>458</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>477</v>
+        <v>459</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8647,13 +8522,11 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8671,7 +8544,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>474</v>
+        <v>455</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8689,27 +8562,27 @@
         <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>478</v>
+        <v>325</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>479</v>
+        <v>326</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8720,7 +8593,7 @@
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>83</v>
@@ -8732,16 +8605,20 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>223</v>
+        <v>84</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>224</v>
+        <v>461</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
       </c>
@@ -8789,19 +8666,19 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>226</v>
+        <v>460</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
@@ -8810,863 +8687,15 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>83</v>
+        <v>375</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>227</v>
+        <v>376</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="Y60" s="2"/>
-      <c r="Z60" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="P62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y63" s="2"/>
-      <c r="Z63" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP64" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -759,6 +759,7 @@
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://loinc.org"/&gt;
   &lt;code value="11524-6"/&gt;
+  &lt;display value="EKG Study"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
@@ -8522,7 +8523,7 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>192</v>
+        <v>313</v>
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2220" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2373" uniqueCount="470">
   <si>
     <t>Property</t>
   </si>
@@ -666,6 +666,99 @@
     <t>FiveWs.class</t>
   </si>
   <si>
+    <t>Observation.category.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.category.extension</t>
+  </si>
+  <si>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+  &lt;code value="procedure"/&gt;
+  &lt;display value="Procedure"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.category.text</t>
+  </si>
+  <si>
+    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
+  </si>
+  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -706,54 +799,10 @@
     <t>Observation.code.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.code.extension</t>
   </si>
   <si>
-    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
     <t>Observation.code.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -763,37 +812,7 @@
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
     <t>Observation.code.text</t>
-  </si>
-  <si>
-    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1782,7 +1801,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP57"/>
+  <dimension ref="A1:AP61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.79296875" customWidth="true" bestFit="true"/>
@@ -3883,11 +3902,11 @@
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>94</v>
@@ -3899,23 +3918,19 @@
         <v>83</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="O18" t="s" s="2">
-        <v>212</v>
-      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>83</v>
       </c>
@@ -3939,11 +3954,13 @@
         <v>83</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y18" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z18" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>83</v>
@@ -3961,10 +3978,10 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>94</v>
@@ -3973,44 +3990,44 @@
         <v>83</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>214</v>
+        <v>83</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>219</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>83</v>
@@ -4022,15 +4039,17 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>221</v>
+        <v>139</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4067,31 +4086,31 @@
         <v>83</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>83</v>
@@ -4103,7 +4122,7 @@
         <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4114,14 +4133,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4137,27 +4156,29 @@
         <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>139</v>
+        <v>220</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>83</v>
+        <v>225</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>83</v>
@@ -4187,19 +4208,19 @@
         <v>83</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>229</v>
+        <v>83</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4211,7 +4232,7 @@
         <v>83</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>83</v>
@@ -4220,10 +4241,10 @@
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4234,10 +4255,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4248,7 +4269,7 @@
         <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>83</v>
@@ -4260,26 +4281,26 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>237</v>
+        <v>83</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>83</v>
@@ -4321,13 +4342,13 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>83</v>
@@ -4342,10 +4363,10 @@
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4356,18 +4377,18 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>83</v>
+        <v>238</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -4382,19 +4403,19 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -4419,13 +4440,11 @@
         <v>83</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>83</v>
+        <v>242</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>83</v>
@@ -4443,10 +4462,10 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>94</v>
@@ -4458,22 +4477,22 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>83</v>
+        <v>243</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>83</v>
+        <v>244</v>
       </c>
       <c r="AM22" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AN22" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AO22" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="23">
@@ -4501,23 +4520,19 @@
         <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>250</v>
+        <v>209</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>253</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>83</v>
       </c>
@@ -4565,7 +4580,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4577,22 +4592,22 @@
         <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>254</v>
+        <v>83</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>255</v>
+        <v>83</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>256</v>
+        <v>213</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>257</v>
+        <v>83</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>83</v>
@@ -4600,14 +4615,14 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4623,19 +4638,19 @@
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>259</v>
+        <v>139</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>260</v>
+        <v>216</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>261</v>
+        <v>161</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4673,19 +4688,19 @@
         <v>83</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>258</v>
+        <v>218</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4697,7 +4712,7 @@
         <v>83</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>83</v>
@@ -4706,13 +4721,13 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>262</v>
+        <v>213</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>257</v>
+        <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>83</v>
@@ -4720,21 +4735,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>264</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>83</v>
@@ -4746,26 +4761,26 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>265</v>
+        <v>220</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>266</v>
+        <v>221</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>266</v>
+        <v>222</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>268</v>
+        <v>224</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>83</v>
+        <v>252</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>83</v>
@@ -4807,13 +4822,13 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>83</v>
@@ -4822,19 +4837,19 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>269</v>
+        <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>270</v>
+        <v>227</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>271</v>
+        <v>228</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>272</v>
+        <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>83</v>
@@ -4842,14 +4857,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>274</v>
+        <v>83</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4868,19 +4883,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>275</v>
+        <v>209</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>276</v>
+        <v>230</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>276</v>
+        <v>231</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>277</v>
+        <v>232</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>278</v>
+        <v>233</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -4929,7 +4944,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>273</v>
+        <v>234</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4944,19 +4959,19 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>280</v>
+        <v>235</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>281</v>
+        <v>236</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>83</v>
@@ -4964,10 +4979,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4990,18 +5005,20 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>284</v>
+        <v>255</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
       </c>
@@ -5049,7 +5066,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5064,19 +5081,19 @@
         <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>83</v>
+        <v>259</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>83</v>
@@ -5084,10 +5101,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5110,20 +5127,18 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>292</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>292</v>
+        <v>265</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>83</v>
       </c>
@@ -5171,7 +5186,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5186,19 +5201,19 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>296</v>
+        <v>245</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>297</v>
+        <v>267</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>298</v>
+        <v>262</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5206,14 +5221,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>83</v>
+        <v>269</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5232,19 +5247,19 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>303</v>
+        <v>273</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5293,7 +5308,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5302,40 +5317,40 @@
         <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>83</v>
+        <v>274</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>305</v>
+        <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>83</v>
+        <v>277</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>308</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>83</v>
+        <v>279</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5351,22 +5366,22 @@
         <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>201</v>
+        <v>280</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5391,13 +5406,13 @@
         <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>315</v>
+        <v>83</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>83</v>
@@ -5415,7 +5430,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5424,25 +5439,25 @@
         <v>94</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>316</v>
+        <v>83</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>83</v>
+        <v>284</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>317</v>
+        <v>286</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>83</v>
@@ -5450,21 +5465,21 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>318</v>
+        <v>288</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>288</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>83</v>
@@ -5473,23 +5488,21 @@
         <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>201</v>
+        <v>289</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>320</v>
+        <v>290</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5513,11 +5526,13 @@
         <v>83</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y31" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z31" t="s" s="2">
-        <v>323</v>
+        <v>83</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>83</v>
@@ -5535,13 +5550,13 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>318</v>
+        <v>288</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>83</v>
@@ -5553,27 +5568,27 @@
         <v>83</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>325</v>
+        <v>292</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>326</v>
+        <v>293</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>327</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5593,22 +5608,22 @@
         <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>329</v>
+        <v>296</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>332</v>
+        <v>299</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5657,7 +5672,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5672,19 +5687,19 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>334</v>
+        <v>302</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>83</v>
+        <v>303</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -5692,10 +5707,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5715,21 +5730,23 @@
         <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>201</v>
+        <v>305</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>336</v>
+        <v>306</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
@@ -5753,13 +5770,13 @@
         <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>338</v>
+        <v>83</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>339</v>
+        <v>83</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>340</v>
+        <v>83</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -5777,7 +5794,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>335</v>
+        <v>304</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5786,7 +5803,7 @@
         <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>106</v>
@@ -5795,27 +5812,27 @@
         <v>83</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>341</v>
+        <v>310</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>342</v>
+        <v>311</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>343</v>
+        <v>312</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>344</v>
+        <v>313</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5841,16 +5858,16 @@
         <v>201</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>346</v>
+        <v>315</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>346</v>
+        <v>315</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>347</v>
+        <v>316</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>348</v>
+        <v>317</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -5875,13 +5892,13 @@
         <v>83</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>349</v>
+        <v>319</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>83</v>
@@ -5899,7 +5916,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>345</v>
+        <v>314</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5908,7 +5925,7 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>83</v>
+        <v>321</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>106</v>
@@ -5920,10 +5937,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>351</v>
+        <v>137</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>352</v>
+        <v>322</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -5934,21 +5951,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -5960,18 +5977,20 @@
         <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>354</v>
+        <v>201</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>355</v>
+        <v>325</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>355</v>
+        <v>325</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -5995,13 +6014,11 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>83</v>
+        <v>328</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -6019,13 +6036,13 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>353</v>
+        <v>323</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
@@ -6037,27 +6054,27 @@
         <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>357</v>
+        <v>329</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>359</v>
+        <v>331</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>360</v>
+        <v>332</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6068,7 +6085,7 @@
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6080,18 +6097,20 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>362</v>
+        <v>334</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>363</v>
+        <v>335</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>363</v>
+        <v>335</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
@@ -6139,13 +6158,13 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>361</v>
+        <v>333</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
@@ -6157,27 +6176,27 @@
         <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>365</v>
+        <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>366</v>
+        <v>338</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>367</v>
+        <v>339</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>368</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6188,7 +6207,7 @@
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>83</v>
@@ -6200,20 +6219,18 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>370</v>
+        <v>201</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>371</v>
+        <v>341</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>371</v>
+        <v>341</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>373</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
@@ -6237,13 +6254,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>83</v>
+        <v>343</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>83</v>
+        <v>344</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>83</v>
+        <v>345</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6261,45 +6278,45 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>374</v>
+        <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>83</v>
+        <v>346</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>376</v>
+        <v>348</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>83</v>
+        <v>349</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>377</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>377</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6322,16 +6339,20 @@
         <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>222</v>
+        <v>351</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6355,13 +6376,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>83</v>
+        <v>343</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>83</v>
+        <v>354</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>83</v>
+        <v>355</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6379,7 +6400,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>224</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6391,7 +6412,7 @@
         <v>83</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>83</v>
@@ -6400,10 +6421,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>225</v>
+        <v>357</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6414,21 +6435,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>83</v>
@@ -6440,16 +6461,16 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>139</v>
+        <v>359</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>227</v>
+        <v>360</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>228</v>
+        <v>360</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>161</v>
+        <v>361</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6499,81 +6520,79 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>230</v>
+        <v>358</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>83</v>
+        <v>362</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>83</v>
+        <v>363</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>225</v>
+        <v>364</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>83</v>
+        <v>365</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>139</v>
+        <v>367</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6621,45 +6640,45 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>83</v>
+        <v>370</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>83</v>
+        <v>371</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>137</v>
+        <v>372</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>83</v>
+        <v>373</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6670,7 +6689,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>83</v>
@@ -6682,16 +6701,20 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
       </c>
@@ -6739,19 +6762,19 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>379</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>83</v>
@@ -6760,10 +6783,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -6774,10 +6797,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6800,13 +6823,13 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>385</v>
+        <v>209</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>392</v>
+        <v>210</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>393</v>
+        <v>211</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6857,7 +6880,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>391</v>
+        <v>212</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6866,10 +6889,10 @@
         <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>388</v>
+        <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -6878,10 +6901,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>394</v>
+        <v>213</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -6892,21 +6915,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>83</v>
@@ -6918,20 +6941,18 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>396</v>
+        <v>215</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>397</v>
+        <v>216</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -6955,13 +6976,13 @@
         <v>83</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>400</v>
+        <v>83</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>401</v>
+        <v>83</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>83</v>
@@ -6979,31 +7000,31 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>395</v>
+        <v>218</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>402</v>
+        <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>403</v>
+        <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>326</v>
+        <v>213</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7014,14 +7035,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7034,25 +7055,25 @@
         <v>83</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>407</v>
+        <v>161</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>408</v>
+        <v>162</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7077,13 +7098,13 @@
         <v>83</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>338</v>
+        <v>83</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>409</v>
+        <v>83</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>410</v>
+        <v>83</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>83</v>
@@ -7101,7 +7122,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7113,19 +7134,19 @@
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>402</v>
+        <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>403</v>
+        <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>326</v>
+        <v>137</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7136,10 +7157,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>411</v>
+        <v>389</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>411</v>
+        <v>389</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7162,18 +7183,16 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>412</v>
+        <v>390</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>413</v>
+        <v>391</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>414</v>
+        <v>392</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>415</v>
-      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
@@ -7221,7 +7240,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>411</v>
+        <v>389</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7230,7 +7249,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>83</v>
+        <v>393</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7242,10 +7261,10 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>416</v>
+        <v>395</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7256,10 +7275,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7282,13 +7301,13 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>221</v>
+        <v>390</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7339,7 +7358,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7348,7 +7367,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>83</v>
+        <v>393</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7360,10 +7379,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7374,10 +7393,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7388,7 +7407,7 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
@@ -7397,21 +7416,23 @@
         <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>422</v>
+        <v>201</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>423</v>
+        <v>401</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>423</v>
+        <v>402</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7435,13 +7456,13 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>83</v>
+        <v>405</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>83</v>
+        <v>406</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7459,13 +7480,13 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
@@ -7477,13 +7498,13 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>83</v>
+        <v>407</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>426</v>
+        <v>331</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7494,10 +7515,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7517,21 +7538,23 @@
         <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>428</v>
+        <v>201</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>412</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7555,13 +7578,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>83</v>
+        <v>343</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>83</v>
+        <v>414</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>83</v>
+        <v>415</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7579,7 +7602,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>427</v>
+        <v>409</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7597,13 +7620,13 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>83</v>
+        <v>407</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>431</v>
+        <v>331</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7614,10 +7637,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7628,7 +7651,7 @@
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>83</v>
@@ -7637,22 +7660,20 @@
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>370</v>
+        <v>417</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>434</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7701,13 +7722,13 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>83</v>
@@ -7722,10 +7743,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>436</v>
+        <v>83</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7736,10 +7757,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7762,13 +7783,13 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>222</v>
+        <v>423</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>223</v>
+        <v>424</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7819,7 +7840,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>224</v>
+        <v>422</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7831,7 +7852,7 @@
         <v>83</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>83</v>
@@ -7840,10 +7861,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>225</v>
+        <v>425</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -7854,14 +7875,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7877,19 +7898,19 @@
         <v>83</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>139</v>
+        <v>427</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>227</v>
+        <v>428</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>228</v>
+        <v>428</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>161</v>
+        <v>429</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7939,7 +7960,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>230</v>
+        <v>426</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -7951,7 +7972,7 @@
         <v>83</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>83</v>
@@ -7960,10 +7981,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>83</v>
+        <v>430</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>225</v>
+        <v>431</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -7974,14 +7995,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7994,26 +8015,24 @@
         <v>83</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>139</v>
+        <v>433</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>381</v>
+        <v>434</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>382</v>
+        <v>434</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>435</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8061,7 +8080,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>383</v>
+        <v>432</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8073,7 +8092,7 @@
         <v>83</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>83</v>
@@ -8082,10 +8101,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>83</v>
+        <v>430</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>137</v>
+        <v>436</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8096,10 +8115,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8107,10 +8126,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>83</v>
@@ -8122,19 +8141,19 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>201</v>
+        <v>375</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>212</v>
+        <v>440</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8159,11 +8178,13 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="Y53" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z53" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8181,13 +8202,13 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>83</v>
@@ -8199,16 +8220,16 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>445</v>
+        <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>216</v>
+        <v>441</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>217</v>
+        <v>442</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>218</v>
+        <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8216,10 +8237,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8239,23 +8260,19 @@
         <v>83</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>300</v>
+        <v>209</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>447</v>
+        <v>210</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
       </c>
@@ -8303,7 +8320,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>446</v>
+        <v>212</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8315,44 +8332,44 @@
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>450</v>
+        <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>306</v>
+        <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>307</v>
+        <v>213</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>308</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>83</v>
@@ -8364,20 +8381,18 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>452</v>
+        <v>215</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>453</v>
+        <v>216</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -8401,13 +8416,13 @@
         <v>83</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>315</v>
+        <v>83</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>83</v>
@@ -8425,19 +8440,19 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>451</v>
+        <v>218</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>316</v>
+        <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8446,10 +8461,10 @@
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>317</v>
+        <v>213</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8460,14 +8475,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>319</v>
+        <v>385</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8480,25 +8495,25 @@
         <v>83</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>456</v>
+        <v>386</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>457</v>
+        <v>387</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>458</v>
+        <v>161</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>459</v>
+        <v>162</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8523,11 +8538,13 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="Y56" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z56" t="s" s="2">
-        <v>323</v>
+        <v>83</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8545,7 +8562,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>455</v>
+        <v>388</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8557,33 +8574,33 @@
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>325</v>
+        <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>326</v>
+        <v>137</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>327</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8591,10 +8608,10 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>83</v>
@@ -8603,22 +8620,22 @@
         <v>83</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>461</v>
+        <v>447</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>462</v>
+        <v>448</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>463</v>
+        <v>449</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>464</v>
+        <v>241</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8643,13 +8660,11 @@
         <v>83</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>83</v>
+        <v>242</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>83</v>
@@ -8667,13 +8682,13 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>83</v>
@@ -8685,18 +8700,504 @@
         <v>83</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>83</v>
+        <v>450</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>375</v>
+        <v>245</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>376</v>
+        <v>246</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>83</v>
+        <v>247</v>
       </c>
       <c r="AP57" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP58" t="s" s="2">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="Y60" s="2"/>
+      <c r="Z60" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2373" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="479">
   <si>
     <t>Property</t>
   </si>
@@ -651,19 +651,38 @@
     <t>Observationリソースに対する分類コード。心電図検査には procedure が指定される。</t>
   </si>
   <si>
+    <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
+  </si>
+  <si>
+    <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:coding.system}
+</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:simpleCategory</t>
+  </si>
+  <si>
+    <t>simpleCategory</t>
+  </si>
+  <si>
+    <t>このObservationを分類するコード</t>
+  </si>
+  <si>
     <t>心電図検査は procedure に分類されている。</t>
   </si>
   <si>
-    <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
+    <t>Observation.category:simpleCategory.id</t>
   </si>
   <si>
     <t>Observation.category.id</t>
@@ -685,6 +704,9 @@
     <t>n/a</t>
   </si>
   <si>
+    <t>Observation.category:simpleCategory.extension</t>
+  </si>
+  <si>
     <t>Observation.category.extension</t>
   </si>
   <si>
@@ -698,6 +720,9 @@
   </si>
   <si>
     <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:simpleCategory.coding</t>
   </si>
   <si>
     <t>Observation.category.coding</t>
@@ -733,6 +758,9 @@
   </si>
   <si>
     <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.category:simpleCategory.text</t>
   </si>
   <si>
     <t>Observation.category.text</t>
@@ -1801,10 +1829,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP61"/>
+  <dimension ref="A1:AP62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.79296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.48828125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="23.4609375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -3838,7 +3866,7 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>192</v>
+        <v>118</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
@@ -3848,16 +3876,14 @@
         <v>83</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="AC17" s="2"/>
       <c r="AD17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>200</v>
@@ -3884,10 +3910,10 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>83</v>
@@ -3895,12 +3921,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>200</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>83</v>
       </c>
@@ -3921,16 +3949,20 @@
         <v>83</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+      <c r="N18" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>83</v>
       </c>
@@ -3954,13 +3986,11 @@
         <v>83</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>83</v>
@@ -3978,19 +4008,19 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>83</v>
@@ -4002,10 +4032,10 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>83</v>
+        <v>208</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -4013,21 +4043,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>83</v>
@@ -4039,17 +4069,15 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>139</v>
+        <v>215</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4086,16 +4114,16 @@
         <v>83</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>218</v>
@@ -4104,13 +4132,13 @@
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>83</v>
@@ -4122,7 +4150,7 @@
         <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4133,14 +4161,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4156,71 +4184,69 @@
         <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4232,7 +4258,7 @@
         <v>83</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>83</v>
@@ -4241,10 +4267,10 @@
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>227</v>
+        <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4255,10 +4281,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4269,7 +4295,7 @@
         <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>83</v>
@@ -4281,26 +4307,26 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>83</v>
+        <v>233</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>83</v>
@@ -4348,7 +4374,7 @@
         <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>83</v>
@@ -4380,15 +4406,15 @@
         <v>237</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>238</v>
+        <v>83</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>94</v>
@@ -4403,19 +4429,19 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>239</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -4440,11 +4466,13 @@
         <v>83</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>242</v>
+        <v>83</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>83</v>
@@ -4462,10 +4490,10 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>94</v>
@@ -4477,38 +4505,38 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>243</v>
+        <v>83</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AN22" t="s" s="2">
-        <v>246</v>
-      </c>
       <c r="AO22" t="s" s="2">
-        <v>247</v>
+        <v>83</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>248</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>83</v>
+        <v>247</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>94</v>
@@ -4520,19 +4548,23 @@
         <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
       </c>
@@ -4556,13 +4588,11 @@
         <v>83</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>83</v>
+        <v>251</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>83</v>
@@ -4580,10 +4610,10 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>94</v>
@@ -4592,44 +4622,44 @@
         <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>83</v>
+        <v>252</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>83</v>
+        <v>253</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>83</v>
+        <v>254</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>213</v>
+        <v>255</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>83</v>
+        <v>256</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>83</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>83</v>
@@ -4641,17 +4671,15 @@
         <v>83</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>139</v>
+        <v>215</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -4688,16 +4716,16 @@
         <v>83</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>218</v>
@@ -4706,13 +4734,13 @@
         <v>81</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>83</v>
@@ -4724,7 +4752,7 @@
         <v>83</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4735,14 +4763,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4758,29 +4786,27 @@
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>252</v>
+        <v>83</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>83</v>
@@ -4810,19 +4836,19 @@
         <v>83</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>83</v>
+        <v>224</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4834,7 +4860,7 @@
         <v>83</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>83</v>
@@ -4843,10 +4869,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>227</v>
+        <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -4857,10 +4883,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4871,7 +4897,7 @@
         <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>83</v>
@@ -4883,26 +4909,26 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>233</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>83</v>
+        <v>261</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>83</v>
@@ -4950,7 +4976,7 @@
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>83</v>
@@ -4979,10 +5005,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5005,19 +5031,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>258</v>
+        <v>242</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5066,7 +5092,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5081,19 +5107,19 @@
         <v>106</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>259</v>
+        <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>261</v>
+        <v>245</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>262</v>
+        <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>83</v>
@@ -5115,7 +5141,7 @@
         <v>81</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>83</v>
@@ -5138,7 +5164,9 @@
       <c r="N28" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="O28" s="2"/>
+      <c r="O28" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
       </c>
@@ -5192,7 +5220,7 @@
         <v>81</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>83</v>
@@ -5201,19 +5229,19 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>83</v>
+        <v>268</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5221,21 +5249,21 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>269</v>
+        <v>83</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>83</v>
@@ -5247,20 +5275,18 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>83</v>
       </c>
@@ -5308,13 +5334,13 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>83</v>
@@ -5323,19 +5349,19 @@
         <v>106</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>274</v>
+        <v>83</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>275</v>
+        <v>254</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>276</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>83</v>
@@ -5343,14 +5369,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5369,19 +5395,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="M30" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5430,7 +5456,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5445,19 +5471,19 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>83</v>
@@ -5465,14 +5491,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5502,7 +5528,9 @@
       <c r="N31" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="O31" s="2"/>
+      <c r="O31" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5550,7 +5578,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5565,19 +5593,19 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>83</v>
@@ -5585,10 +5613,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5599,7 +5627,7 @@
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>83</v>
@@ -5611,20 +5639,18 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
@@ -5672,13 +5698,13 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>83</v>
@@ -5687,7 +5713,7 @@
         <v>106</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>83</v>
@@ -5721,7 +5747,7 @@
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
@@ -5800,39 +5826,39 @@
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>309</v>
+        <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
       <c r="AL33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="AO33" t="s" s="2">
-        <v>83</v>
-      </c>
       <c r="AP33" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5852,10 +5878,10 @@
         <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>201</v>
+        <v>314</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>315</v>
@@ -5892,13 +5918,13 @@
         <v>83</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>320</v>
+        <v>83</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>83</v>
@@ -5916,7 +5942,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5925,7 +5951,7 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>106</v>
@@ -5934,19 +5960,19 @@
         <v>83</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>83</v>
+        <v>319</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>137</v>
+        <v>320</v>
       </c>
       <c r="AN34" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="35">
@@ -5958,14 +5984,14 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -5980,16 +6006,16 @@
         <v>201</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6014,11 +6040,13 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y35" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="Z35" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -6042,10 +6070,10 @@
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>83</v>
+        <v>330</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>106</v>
@@ -6054,10 +6082,10 @@
         <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>329</v>
+        <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>330</v>
+        <v>137</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>331</v>
@@ -6066,19 +6094,19 @@
         <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6097,19 +6125,19 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N36" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M36" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6134,13 +6162,11 @@
         <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -6158,7 +6184,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6176,27 +6202,27 @@
         <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>83</v>
+        <v>338</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>83</v>
+        <v>341</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6207,7 +6233,7 @@
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>83</v>
@@ -6219,18 +6245,20 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>201</v>
+        <v>343</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
@@ -6254,13 +6282,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>343</v>
+        <v>83</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>344</v>
+        <v>83</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>345</v>
+        <v>83</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6278,13 +6306,13 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>83</v>
@@ -6296,7 +6324,7 @@
         <v>83</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>346</v>
+        <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>347</v>
@@ -6308,15 +6336,15 @@
         <v>83</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>349</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6342,17 +6370,15 @@
         <v>201</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="M38" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>353</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6376,14 +6402,14 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="Z38" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="Z38" t="s" s="2">
-        <v>355</v>
-      </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6400,7 +6426,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6418,7 +6444,7 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>83</v>
+        <v>355</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>356</v>
@@ -6430,15 +6456,15 @@
         <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>83</v>
+        <v>358</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6461,7 +6487,7 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>359</v>
+        <v>201</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>360</v>
@@ -6472,7 +6498,9 @@
       <c r="N39" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
@@ -6496,13 +6524,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>83</v>
+        <v>352</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>83</v>
+        <v>363</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>83</v>
+        <v>364</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6520,7 +6548,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6538,27 +6566,27 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>362</v>
+        <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>365</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6581,16 +6609,16 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6640,7 +6668,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6658,27 +6686,27 @@
         <v>83</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6689,7 +6717,7 @@
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>83</v>
@@ -6701,20 +6729,18 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="O41" t="s" s="2">
         <v>378</v>
       </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
       </c>
@@ -6762,25 +6788,25 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>380</v>
@@ -6792,15 +6818,15 @@
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>83</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6811,7 +6837,7 @@
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -6823,16 +6849,20 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>209</v>
+        <v>384</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>210</v>
+        <v>385</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>387</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
       </c>
@@ -6880,19 +6910,19 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>212</v>
+        <v>383</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -6901,10 +6931,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>83</v>
+        <v>389</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>213</v>
+        <v>390</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -6915,21 +6945,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>83</v>
@@ -6941,17 +6971,15 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>139</v>
+        <v>215</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7006,13 +7034,13 @@
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>83</v>
@@ -7024,7 +7052,7 @@
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7035,14 +7063,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>385</v>
+        <v>158</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7055,26 +7083,24 @@
         <v>83</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>386</v>
+        <v>222</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>387</v>
+        <v>223</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="O44" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7122,7 +7148,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>388</v>
+        <v>225</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7146,7 +7172,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>137</v>
+        <v>219</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7157,42 +7183,46 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>390</v>
+        <v>139</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
@@ -7240,19 +7270,19 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>393</v>
+        <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>83</v>
@@ -7261,10 +7291,10 @@
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>394</v>
+        <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>395</v>
+        <v>137</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7275,10 +7305,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7301,13 +7331,13 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7358,7 +7388,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7367,7 +7397,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7379,10 +7409,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7393,10 +7423,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7419,20 +7449,16 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>201</v>
+        <v>399</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7456,31 +7482,31 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF47" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7489,7 +7515,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7498,13 +7524,13 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>407</v>
+        <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7529,7 +7555,7 @@
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7578,7 +7604,7 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>343</v>
+        <v>118</v>
       </c>
       <c r="Y48" t="s" s="2">
         <v>414</v>
@@ -7608,7 +7634,7 @@
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>83</v>
@@ -7620,13 +7646,13 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7637,10 +7663,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7651,7 +7677,7 @@
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>83</v>
@@ -7663,17 +7689,19 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>417</v>
+        <v>201</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>420</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>421</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7698,13 +7726,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>83</v>
+        <v>352</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>83</v>
+        <v>423</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>83</v>
+        <v>424</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7722,13 +7750,13 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>83</v>
@@ -7740,13 +7768,13 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>83</v>
+        <v>416</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>83</v>
+        <v>417</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>421</v>
+        <v>340</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7757,10 +7785,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7783,16 +7811,18 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>209</v>
+        <v>426</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
       </c>
@@ -7840,7 +7870,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7861,10 +7891,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>394</v>
+        <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -7875,10 +7905,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7889,7 +7919,7 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>83</v>
@@ -7898,20 +7928,18 @@
         <v>83</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>427</v>
+        <v>215</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -7960,13 +7988,13 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>83</v>
@@ -7981,10 +8009,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>430</v>
+        <v>403</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -7995,10 +8023,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8021,16 +8049,16 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8080,7 +8108,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8101,10 +8129,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8115,10 +8143,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8141,20 +8169,18 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>375</v>
+        <v>442</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>444</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8202,7 +8228,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8223,10 +8249,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8237,10 +8263,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8251,7 +8277,7 @@
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8260,19 +8286,23 @@
         <v>83</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>209</v>
+        <v>384</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>210</v>
+        <v>447</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
       </c>
@@ -8320,19 +8350,19 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>212</v>
+        <v>446</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>83</v>
@@ -8341,10 +8371,10 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>83</v>
+        <v>450</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>213</v>
+        <v>451</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8355,21 +8385,21 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>83</v>
@@ -8381,17 +8411,15 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>139</v>
+        <v>215</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -8446,13 +8474,13 @@
         <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
@@ -8464,7 +8492,7 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8475,14 +8503,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>385</v>
+        <v>158</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8495,26 +8523,24 @@
         <v>83</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>386</v>
+        <v>222</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>387</v>
+        <v>223</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="O56" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>83</v>
       </c>
@@ -8562,7 +8588,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>388</v>
+        <v>225</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8586,7 +8612,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>137</v>
+        <v>219</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8597,45 +8623,45 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J57" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>447</v>
+        <v>395</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>448</v>
+        <v>396</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>449</v>
+        <v>161</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>241</v>
+        <v>162</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8660,11 +8686,13 @@
         <v>83</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="Y57" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z57" t="s" s="2">
-        <v>242</v>
+        <v>83</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>83</v>
@@ -8682,34 +8710,34 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>446</v>
+        <v>397</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>450</v>
+        <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>245</v>
+        <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>246</v>
+        <v>137</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>247</v>
+        <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -8717,10 +8745,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8728,7 +8756,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>94</v>
@@ -8743,19 +8771,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>305</v>
+        <v>201</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>308</v>
+        <v>250</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -8780,13 +8808,11 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>83</v>
+        <v>251</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -8804,10 +8830,10 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>94</v>
@@ -8822,27 +8848,27 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>311</v>
+        <v>254</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>312</v>
+        <v>255</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>83</v>
+        <v>256</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8862,19 +8888,19 @@
         <v>83</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>201</v>
+        <v>314</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>317</v>
@@ -8902,13 +8928,13 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>320</v>
+        <v>83</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -8926,7 +8952,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -8935,7 +8961,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>321</v>
+        <v>83</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -8944,38 +8970,38 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>83</v>
+        <v>464</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>137</v>
+        <v>320</v>
       </c>
       <c r="AN59" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>83</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>83</v>
@@ -8990,16 +9016,16 @@
         <v>201</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>464</v>
+        <v>326</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9024,11 +9050,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9046,16 +9074,16 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>83</v>
+        <v>330</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9064,10 +9092,10 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>329</v>
+        <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>330</v>
+        <v>137</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>331</v>
@@ -9076,19 +9104,19 @@
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9107,19 +9135,19 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9144,13 +9172,11 @@
         <v>83</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9168,7 +9194,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9186,18 +9212,140 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>83</v>
+        <v>338</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>380</v>
+        <v>339</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>381</v>
+        <v>340</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="474">
   <si>
     <t>Property</t>
   </si>
@@ -660,29 +660,10 @@
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
-</t>
-  </si>
-  <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:simpleCategory</t>
-  </si>
-  <si>
-    <t>simpleCategory</t>
-  </si>
-  <si>
-    <t>このObservationを分類するコード</t>
-  </si>
-  <si>
-    <t>心電図検査は procedure に分類されている。</t>
-  </si>
-  <si>
-    <t>Observation.category:simpleCategory.id</t>
   </si>
   <si>
     <t>Observation.category.id</t>
@@ -704,9 +685,6 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>Observation.category:simpleCategory.extension</t>
-  </si>
-  <si>
     <t>Observation.category.extension</t>
   </si>
   <si>
@@ -720,9 +698,6 @@
   </si>
   <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:simpleCategory.coding</t>
   </si>
   <si>
     <t>Observation.category.coding</t>
@@ -742,6 +717,28 @@
   </si>
   <si>
     <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:simpleCategory</t>
+  </si>
+  <si>
+    <t>simpleCategory</t>
+  </si>
+  <si>
+    <t>心電図検査は procedure に分類されている。</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
@@ -749,18 +746,6 @@
   &lt;code value="procedure"/&gt;
   &lt;display value="Procedure"/&gt;
 &lt;/valueCoding&gt;</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Observation.category:simpleCategory.text</t>
   </si>
   <si>
     <t>Observation.category.text</t>
@@ -1832,7 +1817,7 @@
   <dimension ref="A1:AP62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="45.48828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.79296875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="23.4609375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -3876,14 +3861,16 @@
         <v>83</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AC17" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>200</v>
@@ -3910,10 +3897,10 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>83</v>
@@ -3921,14 +3908,12 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>83</v>
       </c>
@@ -3949,20 +3934,16 @@
         <v>83</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="N18" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>204</v>
-      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>83</v>
       </c>
@@ -3986,11 +3967,13 @@
         <v>83</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y18" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z18" t="s" s="2">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>83</v>
@@ -4008,19 +3991,19 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>83</v>
@@ -4032,10 +4015,10 @@
         <v>83</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -4043,21 +4026,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>83</v>
@@ -4069,15 +4052,17 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N19" s="2"/>
+      <c r="N19" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
@@ -4114,16 +4099,16 @@
         <v>83</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>218</v>
@@ -4132,13 +4117,13 @@
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>83</v>
@@ -4150,7 +4135,7 @@
         <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>83</v>
@@ -4161,14 +4146,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4184,21 +4169,23 @@
         <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>139</v>
+        <v>220</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="N20" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O20" s="2"/>
+      <c r="O20" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
       </c>
@@ -4234,11 +4221,9 @@
         <v>83</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>83</v>
       </c>
@@ -4246,7 +4231,7 @@
         <v>143</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4258,7 +4243,7 @@
         <v>83</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>83</v>
@@ -4267,10 +4252,10 @@
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4281,12 +4266,14 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="D21" t="s" s="2">
         <v>83</v>
       </c>
@@ -4295,7 +4282,7 @@
         <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>83</v>
@@ -4307,26 +4294,26 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>231</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>83</v>
@@ -4344,13 +4331,11 @@
         <v>83</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>83</v>
@@ -4368,7 +4353,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4389,10 +4374,10 @@
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4403,10 +4388,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4429,19 +4414,19 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -4490,7 +4475,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4511,10 +4496,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4525,14 +4510,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4554,16 +4539,16 @@
         <v>201</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -4592,7 +4577,7 @@
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>83</v>
@@ -4610,7 +4595,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>94</v>
@@ -4625,30 +4610,30 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>257</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4671,13 +4656,13 @@
         <v>83</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4728,7 +4713,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4752,7 +4737,7 @@
         <v>83</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4763,10 +4748,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4792,10 +4777,10 @@
         <v>139</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>161</v>
@@ -4839,7 +4824,7 @@
         <v>142</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>83</v>
@@ -4848,7 +4833,7 @@
         <v>143</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4872,7 +4857,7 @@
         <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -4883,10 +4868,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4909,26 +4894,26 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>83</v>
@@ -4970,7 +4955,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4991,10 +4976,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5005,10 +4990,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5031,19 +5016,19 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5092,7 +5077,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5113,10 +5098,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5127,10 +5112,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5153,19 +5138,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5214,7 +5199,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5229,19 +5214,19 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5249,10 +5234,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5275,16 +5260,16 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5334,7 +5319,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5355,13 +5340,13 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>83</v>
@@ -5369,14 +5354,14 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5395,19 +5380,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5456,7 +5441,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5471,19 +5456,19 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>83</v>
@@ -5491,14 +5476,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5517,19 +5502,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -5578,7 +5563,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5593,19 +5578,19 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>83</v>
@@ -5613,10 +5598,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5639,16 +5624,16 @@
         <v>95</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5698,7 +5683,7 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5719,13 +5704,13 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -5733,10 +5718,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5759,19 +5744,19 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
@@ -5820,7 +5805,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5835,19 +5820,19 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -5855,10 +5840,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5881,19 +5866,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -5942,7 +5927,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5951,7 +5936,7 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>106</v>
@@ -5960,27 +5945,27 @@
         <v>83</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6006,16 +5991,16 @@
         <v>201</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6040,13 +6025,13 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -6064,7 +6049,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6073,7 +6058,7 @@
         <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>106</v>
@@ -6088,7 +6073,7 @@
         <v>137</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6099,14 +6084,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6128,16 +6113,16 @@
         <v>201</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6162,11 +6147,11 @@
         <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -6184,7 +6169,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6202,27 +6187,27 @@
         <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6245,19 +6230,19 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6306,7 +6291,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6327,10 +6312,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6341,10 +6326,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6370,13 +6355,13 @@
         <v>201</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6402,13 +6387,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6426,7 +6411,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6444,27 +6429,27 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6490,16 +6475,16 @@
         <v>201</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6524,13 +6509,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6548,7 +6533,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6569,10 +6554,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6583,10 +6568,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6609,16 +6594,16 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6668,7 +6653,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6686,27 +6671,27 @@
         <v>83</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6729,16 +6714,16 @@
         <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6788,7 +6773,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6806,27 +6791,27 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6849,19 +6834,19 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -6910,7 +6895,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6922,7 +6907,7 @@
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -6931,10 +6916,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -6945,10 +6930,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6971,13 +6956,13 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7028,7 +7013,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7052,7 +7037,7 @@
         <v>83</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7063,10 +7048,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7092,10 +7077,10 @@
         <v>139</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>161</v>
@@ -7148,7 +7133,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7172,7 +7157,7 @@
         <v>83</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7183,14 +7168,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7212,10 +7197,10 @@
         <v>139</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>161</v>
@@ -7270,7 +7255,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7305,10 +7290,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7331,13 +7316,13 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7388,7 +7373,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7397,7 +7382,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7409,10 +7394,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7423,10 +7408,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7449,13 +7434,13 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7506,7 +7491,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7515,7 +7500,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7527,10 +7512,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -7541,10 +7526,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7570,16 +7555,16 @@
         <v>201</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7607,10 +7592,10 @@
         <v>118</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7628,7 +7613,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7646,13 +7631,13 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -7663,10 +7648,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7692,16 +7677,16 @@
         <v>201</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7726,13 +7711,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7750,7 +7735,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7768,13 +7753,13 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7785,10 +7770,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7811,17 +7796,17 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -7870,7 +7855,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7894,7 +7879,7 @@
         <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -7905,10 +7890,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7931,13 +7916,13 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7988,7 +7973,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8009,10 +7994,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8023,10 +8008,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8049,16 +8034,16 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8108,7 +8093,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8129,10 +8114,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8143,10 +8128,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8169,16 +8154,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8228,7 +8213,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8249,10 +8234,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8263,10 +8248,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8289,19 +8274,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8350,7 +8335,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8371,10 +8356,10 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8385,10 +8370,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8411,13 +8396,13 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8468,7 +8453,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8492,7 +8477,7 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8503,10 +8488,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8532,10 +8517,10 @@
         <v>139</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>161</v>
@@ -8588,7 +8573,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8612,7 +8597,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8623,14 +8608,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8652,10 +8637,10 @@
         <v>139</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>161</v>
@@ -8710,7 +8695,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8745,10 +8730,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8774,16 +8759,16 @@
         <v>201</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -8812,7 +8797,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -8830,7 +8815,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>94</v>
@@ -8848,16 +8833,16 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -8865,10 +8850,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8891,19 +8876,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -8952,7 +8937,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -8970,27 +8955,27 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9016,16 +9001,16 @@
         <v>201</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9050,13 +9035,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9074,7 +9059,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9083,7 +9068,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9098,7 +9083,7 @@
         <v>137</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9109,14 +9094,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9138,16 +9123,16 @@
         <v>201</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9172,11 +9157,11 @@
         <v>83</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9194,7 +9179,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9212,27 +9197,27 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9258,16 +9243,16 @@
         <v>84</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9316,7 +9301,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9337,10 +9322,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2678" uniqueCount="523">
   <si>
     <t>Property</t>
   </si>
@@ -741,11 +741,155 @@
     <t>心電図検査は procedure に分類されている。</t>
   </si>
   <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
-  &lt;code value="procedure"/&gt;
-  &lt;display value="Procedure"/&gt;
-&lt;/valueCoding&gt;</t>
+    <t>Observation.category.coding:simpleCategory.id</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:simpleCategory.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:simpleCategory.system</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.system</t>
+  </si>
+  <si>
+    <t>用語システムのアイデンティティ / Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>コード内のシンボルの意味を定義するコードシステムの識別。 / The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:simpleCategory.version</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.version</t>
+  </si>
+  <si>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:simpleCategory.code</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.code</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル / Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>システムによって定義された構文のシンボル。シンボルは、定義されたコードまたはコーディングシステムによって定義された構文の式（例：調整後）である場合があります。 / A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>procedure</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:simpleCategory.display</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.display</t>
+  </si>
+  <si>
+    <t>システムによって定義された表現 / Representation defined by the system</t>
+  </si>
+  <si>
+    <t>システムのルールに従って、システム内のコードの意味の表現。 / A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Procedure</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:simpleCategory.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.userSelected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択された場合 / If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>このコーディングがユーザーによって直接選択されたことを示します。利用可能なアイテムのピックリスト（コードまたはディスプレイ）。 / Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>一連の代替案の中で、直接選択されたコードが新しい翻訳の最も適切な出発点です。この要素の使用とその結果をより完全に明確にするためには、「直接選択された」ことについては曖昧さがあり、取引パートナー契約が必要になる場合があります。 / Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>これは、臨床安全基準として特定されています - この正確なシステム/コードペアは、いくつかのルールまたは言語処理に基づいてシステムによって推測されるのではなく、明示的に選択されたことです。 / This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
   </si>
   <si>
     <t>Observation.category.text</t>
@@ -1814,10 +1958,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP62"/>
+  <dimension ref="A1:AP69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.79296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="55.17578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="23.4609375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -4313,7 +4457,7 @@
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>232</v>
+        <v>83</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>83</v>
@@ -4388,7 +4532,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>233</v>
@@ -4411,23 +4555,19 @@
         <v>83</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K22" t="s" s="2">
         <v>209</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>237</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
@@ -4475,7 +4615,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4487,7 +4627,7 @@
         <v>83</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>83</v>
@@ -4496,10 +4636,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>239</v>
+        <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4510,21 +4650,21 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>242</v>
+        <v>158</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>83</v>
@@ -4533,23 +4673,21 @@
         <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>216</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>83</v>
       </c>
@@ -4573,67 +4711,69 @@
         <v>83</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>246</v>
+        <v>83</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>247</v>
+        <v>83</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>248</v>
+        <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>249</v>
+        <v>83</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>252</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4641,7 +4781,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
@@ -4653,25 +4793,29 @@
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>209</v>
+        <v>108</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>210</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>83</v>
+        <v>242</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4713,7 +4857,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4725,7 +4869,7 @@
         <v>83</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>83</v>
@@ -4734,10 +4878,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>83</v>
+        <v>244</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>213</v>
+        <v>245</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4748,21 +4892,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>83</v>
@@ -4771,19 +4915,19 @@
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>215</v>
+        <v>248</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>161</v>
+        <v>250</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4821,31 +4965,31 @@
         <v>83</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>218</v>
+        <v>251</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>83</v>
@@ -4854,10 +4998,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>83</v>
+        <v>252</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -4868,7 +5012,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>255</v>
@@ -4882,7 +5026,7 @@
         <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>83</v>
@@ -4894,26 +5038,24 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>220</v>
+        <v>114</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>221</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>83</v>
@@ -4955,13 +5097,13 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>83</v>
@@ -4976,10 +5118,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>227</v>
+        <v>261</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>228</v>
+        <v>262</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -4990,10 +5132,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5019,23 +5161,21 @@
         <v>209</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>234</v>
+        <v>265</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>83</v>
+        <v>268</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>83</v>
@@ -5077,7 +5217,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>238</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5098,10 +5238,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>239</v>
+        <v>270</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5112,10 +5252,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5138,19 +5278,19 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -5199,7 +5339,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5214,19 +5354,19 @@
         <v>106</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>263</v>
+        <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>266</v>
+        <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5234,10 +5374,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5248,7 +5388,7 @@
         <v>81</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>83</v>
@@ -5260,18 +5400,20 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
       </c>
@@ -5319,13 +5461,13 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>83</v>
@@ -5340,13 +5482,13 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>249</v>
+        <v>288</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>266</v>
+        <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>83</v>
@@ -5354,18 +5496,18 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>94</v>
@@ -5380,19 +5522,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>274</v>
+        <v>201</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5417,13 +5559,11 @@
         <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>83</v>
@@ -5441,10 +5581,10 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>94</v>
@@ -5456,34 +5596,34 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>83</v>
+        <v>297</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>83</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>283</v>
+        <v>83</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5499,23 +5639,19 @@
         <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>284</v>
+        <v>209</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>285</v>
+        <v>210</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>287</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5563,7 +5699,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>282</v>
+        <v>212</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5575,22 +5711,22 @@
         <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>290</v>
+        <v>213</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>83</v>
@@ -5598,21 +5734,21 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>83</v>
@@ -5621,19 +5757,19 @@
         <v>83</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>293</v>
+        <v>139</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>294</v>
+        <v>215</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>294</v>
+        <v>216</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>295</v>
+        <v>161</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5671,31 +5807,31 @@
         <v>83</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>292</v>
+        <v>218</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>83</v>
@@ -5704,13 +5840,13 @@
         <v>83</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>296</v>
+        <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>297</v>
+        <v>213</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>83</v>
@@ -5718,10 +5854,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5744,26 +5880,26 @@
         <v>95</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>300</v>
+        <v>220</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>301</v>
+        <v>221</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>301</v>
+        <v>222</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>302</v>
+        <v>223</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>303</v>
+        <v>224</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>83</v>
@@ -5805,7 +5941,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>299</v>
+        <v>226</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5820,19 +5956,19 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>305</v>
+        <v>227</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>306</v>
+        <v>228</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>307</v>
+        <v>83</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -5840,10 +5976,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5866,19 +6002,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>309</v>
+        <v>209</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>311</v>
+        <v>285</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -5927,7 +6063,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5936,7 +6072,7 @@
         <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>106</v>
@@ -5945,27 +6081,27 @@
         <v>83</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>315</v>
+        <v>288</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>316</v>
+        <v>289</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5985,22 +6121,22 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>201</v>
+        <v>308</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6025,13 +6161,13 @@
         <v>83</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>322</v>
+        <v>83</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>323</v>
+        <v>83</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>83</v>
@@ -6049,7 +6185,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6058,25 +6194,25 @@
         <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>325</v>
+        <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>83</v>
+        <v>312</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>137</v>
+        <v>313</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>83</v>
+        <v>315</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
@@ -6084,14 +6220,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>328</v>
+        <v>83</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6107,23 +6243,21 @@
         <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
@@ -6147,11 +6281,13 @@
         <v>83</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>83</v>
@@ -6169,7 +6305,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6187,38 +6323,38 @@
         <v>83</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>333</v>
+        <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>334</v>
+        <v>298</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>83</v>
+        <v>315</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>336</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>83</v>
+        <v>322</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>83</v>
@@ -6227,22 +6363,22 @@
         <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6291,13 +6427,13 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>83</v>
@@ -6306,19 +6442,19 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>342</v>
+        <v>328</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>83</v>
+        <v>330</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>83</v>
@@ -6326,14 +6462,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6349,21 +6485,23 @@
         <v>83</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>201</v>
+        <v>333</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6387,13 +6525,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>348</v>
+        <v>83</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>349</v>
+        <v>83</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6411,7 +6549,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6426,30 +6564,30 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>83</v>
+        <v>337</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>350</v>
+        <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>83</v>
+        <v>340</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>353</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6469,23 +6607,21 @@
         <v>83</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>201</v>
+        <v>342</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
@@ -6509,13 +6645,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>358</v>
+        <v>83</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>359</v>
+        <v>83</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6533,7 +6669,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6554,13 +6690,13 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>83</v>
+        <v>347</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -6568,10 +6704,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6582,7 +6718,7 @@
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>83</v>
@@ -6591,21 +6727,23 @@
         <v>83</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6653,13 +6791,13 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>83</v>
@@ -6668,30 +6806,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>83</v>
+        <v>353</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>369</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6711,21 +6849,23 @@
         <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
       </c>
@@ -6773,7 +6913,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6782,7 +6922,7 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>83</v>
+        <v>362</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>106</v>
@@ -6791,27 +6931,27 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>375</v>
+        <v>364</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>377</v>
+        <v>366</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6822,7 +6962,7 @@
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -6834,19 +6974,19 @@
         <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>379</v>
+        <v>201</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -6871,13 +7011,13 @@
         <v>83</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>83</v>
+        <v>371</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>83</v>
+        <v>372</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>83</v>
+        <v>373</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>83</v>
@@ -6895,19 +7035,19 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>83</v>
+        <v>374</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>383</v>
+        <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -6916,10 +7056,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>384</v>
+        <v>137</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -6930,21 +7070,21 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>83</v>
+        <v>377</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>83</v>
@@ -6956,16 +7096,20 @@
         <v>83</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>210</v>
+        <v>378</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>380</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -6989,13 +7133,11 @@
         <v>83</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>83</v>
+        <v>381</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>83</v>
@@ -7013,49 +7155,49 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>212</v>
+        <v>376</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>83</v>
+        <v>382</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>83</v>
+        <v>383</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>213</v>
+        <v>384</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7074,18 +7216,20 @@
         <v>83</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>139</v>
+        <v>387</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>215</v>
+        <v>388</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>216</v>
+        <v>388</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>390</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7133,7 +7277,7 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>218</v>
+        <v>386</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7145,7 +7289,7 @@
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7154,10 +7298,10 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>213</v>
+        <v>392</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7168,46 +7312,44 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>139</v>
+        <v>201</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
@@ -7231,13 +7373,13 @@
         <v>83</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>83</v>
+        <v>397</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>83</v>
+        <v>398</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>83</v>
@@ -7255,45 +7397,45 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>83</v>
+        <v>399</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>137</v>
+        <v>401</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>83</v>
+        <v>402</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7316,16 +7458,20 @@
         <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>394</v>
+        <v>201</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7349,13 +7495,13 @@
         <v>83</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>83</v>
+        <v>407</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>83</v>
+        <v>408</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>83</v>
@@ -7373,7 +7519,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7382,7 +7528,7 @@
         <v>94</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>397</v>
+        <v>83</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>106</v>
@@ -7394,10 +7540,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7408,10 +7554,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7434,15 +7580,17 @@
         <v>83</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7491,7 +7639,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7500,7 +7648,7 @@
         <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>397</v>
+        <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>106</v>
@@ -7509,27 +7657,27 @@
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>83</v>
+        <v>415</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>83</v>
+        <v>418</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7552,20 +7700,18 @@
         <v>83</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>201</v>
+        <v>420</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7589,13 +7735,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>409</v>
+        <v>83</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>410</v>
+        <v>83</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7613,7 +7759,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7631,27 +7777,27 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>335</v>
+        <v>425</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>83</v>
+        <v>426</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7674,19 +7820,19 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>201</v>
+        <v>428</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>414</v>
+        <v>429</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7711,13 +7857,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>418</v>
+        <v>83</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>419</v>
+        <v>83</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7735,7 +7881,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7747,19 +7893,19 @@
         <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>106</v>
+        <v>432</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>335</v>
+        <v>434</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7770,10 +7916,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7796,18 +7942,16 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>421</v>
+        <v>209</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>422</v>
+        <v>210</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>423</v>
+        <v>211</v>
       </c>
       <c r="N50" s="2"/>
-      <c r="O50" t="s" s="2">
-        <v>424</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>83</v>
       </c>
@@ -7855,7 +7999,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>420</v>
+        <v>212</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7867,7 +8011,7 @@
         <v>83</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>83</v>
@@ -7879,7 +8023,7 @@
         <v>83</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>425</v>
+        <v>213</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -7890,21 +8034,21 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>83</v>
@@ -7916,15 +8060,17 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>427</v>
+        <v>215</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -7973,19 +8119,19 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>426</v>
+        <v>218</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>83</v>
@@ -7994,10 +8140,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>398</v>
+        <v>83</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>429</v>
+        <v>213</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8008,14 +8154,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>83</v>
+        <v>438</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8028,24 +8174,26 @@
         <v>83</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J52" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>431</v>
+        <v>139</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8093,7 +8241,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8105,7 +8253,7 @@
         <v>83</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>83</v>
@@ -8114,10 +8262,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>434</v>
+        <v>83</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>435</v>
+        <v>137</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8128,10 +8276,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8142,7 +8290,7 @@
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>83</v>
@@ -8151,20 +8299,18 @@
         <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>83</v>
@@ -8213,16 +8359,16 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>83</v>
+        <v>446</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -8234,10 +8380,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8248,10 +8394,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8262,7 +8408,7 @@
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8271,23 +8417,19 @@
         <v>83</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>379</v>
+        <v>443</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>444</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
       </c>
@@ -8335,16 +8477,16 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>83</v>
+        <v>446</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -8356,10 +8498,10 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8370,10 +8512,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8396,16 +8538,20 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>210</v>
+        <v>454</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -8429,13 +8575,13 @@
         <v>83</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>83</v>
+        <v>458</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>83</v>
+        <v>459</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>83</v>
@@ -8453,7 +8599,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>212</v>
+        <v>453</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8465,19 +8611,19 @@
         <v>83</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>83</v>
+        <v>460</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>83</v>
+        <v>461</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>213</v>
+        <v>384</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8488,14 +8634,14 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8514,18 +8660,20 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>139</v>
+        <v>201</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>215</v>
+        <v>463</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>216</v>
+        <v>464</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
       </c>
@@ -8549,13 +8697,13 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>83</v>
+        <v>467</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>83</v>
+        <v>468</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8573,7 +8721,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>218</v>
+        <v>462</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8585,19 +8733,19 @@
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>83</v>
+        <v>460</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>83</v>
+        <v>461</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>213</v>
+        <v>384</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8608,45 +8756,43 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>139</v>
+        <v>470</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>390</v>
+        <v>471</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>162</v>
+        <v>473</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8695,19 +8841,19 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>392</v>
+        <v>469</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
@@ -8719,7 +8865,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>137</v>
+        <v>474</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8730,10 +8876,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8741,7 +8887,7 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>94</v>
@@ -8753,23 +8899,19 @@
         <v>83</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>477</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>83</v>
       </c>
@@ -8793,11 +8935,13 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y58" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>246</v>
+        <v>83</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -8815,10 +8959,10 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="AG58" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
         <v>94</v>
@@ -8833,16 +8977,16 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>454</v>
+        <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>249</v>
+        <v>447</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>250</v>
+        <v>478</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>83</v>
@@ -8850,10 +8994,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>455</v>
+        <v>479</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>455</v>
+        <v>479</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8864,7 +9008,7 @@
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>83</v>
@@ -8876,20 +9020,18 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>309</v>
+        <v>480</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>457</v>
+        <v>481</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
@@ -8937,13 +9079,13 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>455</v>
+        <v>479</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>83</v>
@@ -8955,27 +9097,27 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>459</v>
+        <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>315</v>
+        <v>483</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>316</v>
+        <v>484</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8986,7 +9128,7 @@
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>83</v>
@@ -8995,23 +9137,21 @@
         <v>83</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>201</v>
+        <v>486</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>461</v>
+        <v>487</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>462</v>
+        <v>487</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
@@ -9035,13 +9175,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>322</v>
+        <v>83</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>323</v>
+        <v>83</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9059,16 +9199,16 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>325</v>
+        <v>83</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9080,10 +9220,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>137</v>
+        <v>483</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9094,14 +9234,14 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>328</v>
+        <v>83</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9117,22 +9257,22 @@
         <v>83</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>201</v>
+        <v>428</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>465</v>
+        <v>491</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9157,11 +9297,13 @@
         <v>83</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>83</v>
@@ -9179,7 +9321,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>464</v>
+        <v>490</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9197,27 +9339,27 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>333</v>
+        <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>334</v>
+        <v>494</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>335</v>
+        <v>495</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>336</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9228,7 +9370,7 @@
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>83</v>
@@ -9240,20 +9382,16 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>84</v>
+        <v>209</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>470</v>
+        <v>210</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9301,36 +9439,884 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>469</v>
+        <v>212</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP62" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G63" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AI62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
+      <c r="H63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y65" s="2"/>
+      <c r="Z65" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM62" t="s" s="2">
+      <c r="AK65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="P67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="Y68" s="2"/>
+      <c r="Z68" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AN62" t="s" s="2">
+      <c r="AO68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AO62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP62" t="s" s="2">
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -488,13 +488,13 @@
 </t>
   </si>
   <si>
-    <t>Observation.extension:machinaryInterpretation</t>
-  </si>
-  <si>
-    <t>machinaryInterpretation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_MachinaryInterpretation}
+    <t>Observation.extension:deviceInterpretation</t>
+  </si>
+  <si>
+    <t>deviceInterpretation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_DeviceInterpretation}
 </t>
   </si>
   <si>
@@ -1963,7 +1963,7 @@
   <cols>
     <col min="1" max="1" width="55.17578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="23.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.76953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2678" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="532">
   <si>
     <t>Property</t>
   </si>
@@ -962,11 +962,34 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://loinc.org"/&gt;
-  &lt;code value="11524-6"/&gt;
-  &lt;display value="EKG Study"/&gt;
-&lt;/valueCoding&gt;</t>
+    <t>Observation.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>Loinc_CS</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.code</t>
+  </si>
+  <si>
+    <t>11524-6</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.display</t>
+  </si>
+  <si>
+    <t>EKG Study</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1958,7 +1981,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP69"/>
+  <dimension ref="A1:AP76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.17578125" customWidth="true" bestFit="true"/>
@@ -5899,7 +5922,7 @@
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>305</v>
+        <v>83</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>83</v>
@@ -5976,10 +5999,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5999,23 +6022,19 @@
         <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>209</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>283</v>
+        <v>210</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
@@ -6063,7 +6082,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>287</v>
+        <v>212</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6075,7 +6094,7 @@
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>83</v>
@@ -6084,10 +6103,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>289</v>
+        <v>213</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6098,21 +6117,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -6121,23 +6140,21 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>308</v>
+        <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>309</v>
+        <v>215</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>309</v>
+        <v>216</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>311</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6173,46 +6190,46 @@
         <v>83</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>307</v>
+        <v>218</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>312</v>
+        <v>83</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>314</v>
+        <v>213</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>315</v>
+        <v>83</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>83</v>
@@ -6220,10 +6237,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6234,7 +6251,7 @@
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6246,24 +6263,26 @@
         <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>317</v>
+        <v>108</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>318</v>
+        <v>238</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>318</v>
+        <v>239</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>83</v>
+        <v>308</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6305,13 +6324,13 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>243</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
@@ -6326,13 +6345,13 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>320</v>
+        <v>245</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>315</v>
+        <v>83</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>83</v>
@@ -6340,14 +6359,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>322</v>
+        <v>83</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6366,20 +6385,18 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>323</v>
+        <v>209</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>324</v>
+        <v>248</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>324</v>
+        <v>249</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
@@ -6427,7 +6444,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>251</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6442,19 +6459,19 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>327</v>
+        <v>83</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>328</v>
+        <v>252</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>329</v>
+        <v>253</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>330</v>
+        <v>83</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>83</v>
@@ -6462,14 +6479,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>332</v>
+        <v>83</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6488,26 +6505,24 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>333</v>
+        <v>114</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>334</v>
+        <v>256</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>336</v>
+        <v>258</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>83</v>
+        <v>311</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>83</v>
@@ -6549,7 +6564,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>331</v>
+        <v>260</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6564,19 +6579,19 @@
         <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>337</v>
+        <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>338</v>
+        <v>261</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>339</v>
+        <v>262</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>340</v>
+        <v>83</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>83</v>
@@ -6584,10 +6599,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6610,18 +6625,18 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>342</v>
+        <v>209</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>343</v>
+        <v>265</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
@@ -6630,7 +6645,7 @@
         <v>83</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>83</v>
+        <v>313</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>83</v>
@@ -6669,7 +6684,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>269</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6690,13 +6705,13 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>345</v>
+        <v>270</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>346</v>
+        <v>271</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>83</v>
@@ -6704,10 +6719,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>348</v>
+        <v>314</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>348</v>
+        <v>314</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6718,7 +6733,7 @@
         <v>81</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>83</v>
@@ -6730,19 +6745,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>349</v>
+        <v>274</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>350</v>
+        <v>275</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>350</v>
+        <v>276</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>351</v>
+        <v>277</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>352</v>
+        <v>278</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6791,13 +6806,13 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>348</v>
+        <v>279</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>83</v>
@@ -6806,19 +6821,19 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>353</v>
+        <v>83</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>354</v>
+        <v>280</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>355</v>
+        <v>281</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>356</v>
+        <v>83</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>83</v>
@@ -6826,10 +6841,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>315</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>315</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6852,19 +6867,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>358</v>
+        <v>209</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>359</v>
+        <v>283</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>359</v>
+        <v>284</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>360</v>
+        <v>285</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>361</v>
+        <v>286</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6913,7 +6928,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>357</v>
+        <v>287</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6922,7 +6937,7 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>362</v>
+        <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>106</v>
@@ -6931,27 +6946,27 @@
         <v>83</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>363</v>
+        <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>364</v>
+        <v>288</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>365</v>
+        <v>289</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>367</v>
+        <v>316</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>367</v>
+        <v>316</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6971,22 +6986,22 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>368</v>
+        <v>318</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>368</v>
+        <v>318</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>369</v>
+        <v>319</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>370</v>
+        <v>320</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7011,13 +7026,13 @@
         <v>83</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>373</v>
+        <v>83</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>83</v>
@@ -7035,7 +7050,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>367</v>
+        <v>316</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7044,25 +7059,25 @@
         <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>374</v>
+        <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>83</v>
+        <v>321</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>137</v>
+        <v>322</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>375</v>
+        <v>323</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7070,14 +7085,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7093,23 +7108,21 @@
         <v>83</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>201</v>
+        <v>326</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>378</v>
+        <v>327</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>378</v>
+        <v>327</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7133,11 +7146,13 @@
         <v>83</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>83</v>
@@ -7155,7 +7170,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7173,38 +7188,38 @@
         <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>383</v>
+        <v>298</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>384</v>
+        <v>329</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>385</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>83</v>
+        <v>331</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -7213,22 +7228,22 @@
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>387</v>
+        <v>332</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>388</v>
+        <v>333</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>388</v>
+        <v>333</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>389</v>
+        <v>334</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>390</v>
+        <v>335</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7277,13 +7292,13 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>386</v>
+        <v>330</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
@@ -7292,19 +7307,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>83</v>
+        <v>336</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>391</v>
+        <v>337</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>392</v>
+        <v>338</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>83</v>
+        <v>339</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7312,14 +7327,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>393</v>
+        <v>340</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>393</v>
+        <v>340</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>83</v>
+        <v>341</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7335,21 +7350,23 @@
         <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>201</v>
+        <v>342</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>394</v>
+        <v>343</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>394</v>
+        <v>343</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
       </c>
@@ -7373,13 +7390,13 @@
         <v>83</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>397</v>
+        <v>83</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>398</v>
+        <v>83</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>83</v>
@@ -7397,7 +7414,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>393</v>
+        <v>340</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7412,30 +7429,30 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>83</v>
+        <v>346</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>399</v>
+        <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>400</v>
+        <v>347</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>401</v>
+        <v>348</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>83</v>
+        <v>349</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>402</v>
+        <v>83</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>403</v>
+        <v>350</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>403</v>
+        <v>350</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7455,23 +7472,21 @@
         <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>201</v>
+        <v>351</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>404</v>
+        <v>352</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>404</v>
+        <v>352</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7495,13 +7510,13 @@
         <v>83</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>407</v>
+        <v>83</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>408</v>
+        <v>83</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>83</v>
@@ -7519,7 +7534,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>403</v>
+        <v>350</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7540,13 +7555,13 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>409</v>
+        <v>354</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>410</v>
+        <v>355</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7554,10 +7569,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>357</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>357</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7568,7 +7583,7 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
@@ -7577,21 +7592,23 @@
         <v>83</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>412</v>
+        <v>358</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>413</v>
+        <v>359</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>413</v>
+        <v>359</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7639,13 +7656,13 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>411</v>
+        <v>357</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
@@ -7654,30 +7671,30 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>83</v>
+        <v>362</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>416</v>
+        <v>363</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>417</v>
+        <v>364</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>83</v>
+        <v>365</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>418</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>419</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>419</v>
+        <v>366</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7697,21 +7714,23 @@
         <v>83</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>420</v>
+        <v>367</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>421</v>
+        <v>368</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>421</v>
+        <v>368</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
@@ -7759,7 +7778,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>419</v>
+        <v>366</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7768,7 +7787,7 @@
         <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>83</v>
+        <v>371</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
@@ -7777,27 +7796,27 @@
         <v>83</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>423</v>
+        <v>372</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>426</v>
+        <v>375</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>427</v>
+        <v>376</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>427</v>
+        <v>376</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7808,7 +7827,7 @@
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>83</v>
@@ -7820,19 +7839,19 @@
         <v>83</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>428</v>
+        <v>201</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>429</v>
+        <v>377</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>429</v>
+        <v>377</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>430</v>
+        <v>378</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>431</v>
+        <v>379</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7857,13 +7876,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>83</v>
+        <v>380</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>83</v>
+        <v>381</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>83</v>
+        <v>382</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7881,19 +7900,19 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>427</v>
+        <v>376</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>83</v>
+        <v>383</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>432</v>
+        <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>83</v>
@@ -7902,10 +7921,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>433</v>
+        <v>137</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>434</v>
+        <v>384</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -7916,21 +7935,21 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>435</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>435</v>
+        <v>385</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>83</v>
+        <v>386</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -7942,16 +7961,20 @@
         <v>83</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>210</v>
+        <v>387</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
       </c>
@@ -7975,13 +7998,11 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>83</v>
+        <v>390</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -7999,49 +8020,49 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>212</v>
+        <v>385</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>83</v>
+        <v>391</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>83</v>
+        <v>392</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>213</v>
+        <v>393</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>436</v>
+        <v>395</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>436</v>
+        <v>395</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8060,18 +8081,20 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>139</v>
+        <v>396</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>215</v>
+        <v>397</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>216</v>
+        <v>397</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>398</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>399</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
       </c>
@@ -8119,7 +8142,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>218</v>
+        <v>395</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8131,7 +8154,7 @@
         <v>83</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>83</v>
@@ -8140,10 +8163,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>213</v>
+        <v>401</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8154,46 +8177,44 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>437</v>
+        <v>402</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>437</v>
+        <v>402</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>438</v>
+        <v>83</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>139</v>
+        <v>201</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>439</v>
+        <v>403</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>440</v>
+        <v>403</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8217,13 +8238,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>83</v>
+        <v>405</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>83</v>
+        <v>406</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>83</v>
+        <v>407</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8241,45 +8262,45 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>441</v>
+        <v>402</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>83</v>
+        <v>408</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>83</v>
+        <v>409</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>137</v>
+        <v>410</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>83</v>
+        <v>411</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>442</v>
+        <v>412</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>442</v>
+        <v>412</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8302,16 +8323,20 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>443</v>
+        <v>201</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>444</v>
+        <v>413</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>415</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8335,13 +8360,13 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>83</v>
+        <v>405</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>83</v>
+        <v>416</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>83</v>
+        <v>417</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8359,7 +8384,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>442</v>
+        <v>412</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8368,7 +8393,7 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>446</v>
+        <v>83</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -8380,10 +8405,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>447</v>
+        <v>418</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>448</v>
+        <v>419</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8394,10 +8419,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8420,15 +8445,17 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>422</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8477,7 +8504,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8486,7 +8513,7 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>446</v>
+        <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>106</v>
@@ -8495,27 +8522,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>83</v>
+        <v>424</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>83</v>
+        <v>427</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>453</v>
+        <v>428</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>453</v>
+        <v>428</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8538,20 +8565,18 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>201</v>
+        <v>429</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -8575,13 +8600,13 @@
         <v>83</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>458</v>
+        <v>83</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>459</v>
+        <v>83</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>83</v>
@@ -8599,7 +8624,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>453</v>
+        <v>428</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8617,27 +8642,27 @@
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>460</v>
+        <v>432</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>461</v>
+        <v>433</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>384</v>
+        <v>434</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>83</v>
+        <v>435</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8660,19 +8685,19 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>201</v>
+        <v>437</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>464</v>
+        <v>438</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8697,13 +8722,13 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>467</v>
+        <v>83</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>468</v>
+        <v>83</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8721,7 +8746,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8733,19 +8758,19 @@
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>441</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>460</v>
+        <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>384</v>
+        <v>443</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -8756,10 +8781,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8782,18 +8807,16 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>470</v>
+        <v>209</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>471</v>
+        <v>210</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>472</v>
+        <v>211</v>
       </c>
       <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>473</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>83</v>
       </c>
@@ -8841,7 +8864,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>469</v>
+        <v>212</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8853,7 +8876,7 @@
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
@@ -8865,7 +8888,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>474</v>
+        <v>213</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8876,21 +8899,21 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>475</v>
+        <v>445</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>83</v>
@@ -8902,15 +8925,17 @@
         <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>476</v>
+        <v>215</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>477</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -8959,19 +8984,19 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>475</v>
+        <v>218</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>83</v>
@@ -8980,10 +9005,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>447</v>
+        <v>83</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>478</v>
+        <v>213</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -8994,14 +9019,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>83</v>
+        <v>447</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9014,24 +9039,26 @@
         <v>83</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>480</v>
+        <v>139</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>481</v>
+        <v>448</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>481</v>
+        <v>449</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9079,7 +9106,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>479</v>
+        <v>450</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9091,7 +9118,7 @@
         <v>83</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>83</v>
@@ -9100,10 +9127,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>483</v>
+        <v>83</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>484</v>
+        <v>137</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9114,10 +9141,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>485</v>
+        <v>451</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>485</v>
+        <v>451</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9128,7 +9155,7 @@
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>83</v>
@@ -9137,20 +9164,18 @@
         <v>83</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>486</v>
+        <v>452</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>487</v>
+        <v>453</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9199,16 +9224,16 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>485</v>
+        <v>451</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>83</v>
+        <v>455</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9220,10 +9245,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>483</v>
+        <v>456</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>489</v>
+        <v>457</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9234,10 +9259,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9248,7 +9273,7 @@
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>83</v>
@@ -9257,23 +9282,19 @@
         <v>83</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>491</v>
+        <v>459</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>83</v>
       </c>
@@ -9321,16 +9342,16 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>490</v>
+        <v>458</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>83</v>
+        <v>455</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9342,10 +9363,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>494</v>
+        <v>456</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>495</v>
+        <v>461</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9356,10 +9377,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>496</v>
+        <v>462</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9382,16 +9403,20 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>210</v>
+        <v>463</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9415,13 +9440,13 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>83</v>
+        <v>467</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>83</v>
+        <v>468</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9439,7 +9464,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>212</v>
+        <v>462</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9451,19 +9476,19 @@
         <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>83</v>
+        <v>469</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>83</v>
+        <v>470</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>213</v>
+        <v>393</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9474,14 +9499,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>497</v>
+        <v>471</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>497</v>
+        <v>471</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9500,18 +9525,20 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>139</v>
+        <v>201</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>215</v>
+        <v>472</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>216</v>
+        <v>473</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>474</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
       </c>
@@ -9535,13 +9562,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>83</v>
+        <v>405</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>83</v>
+        <v>476</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>83</v>
+        <v>477</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9559,7 +9586,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>218</v>
+        <v>471</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9571,19 +9598,19 @@
         <v>83</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>83</v>
+        <v>469</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>83</v>
+        <v>470</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>213</v>
+        <v>393</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9594,45 +9621,43 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>438</v>
+        <v>83</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>139</v>
+        <v>479</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>439</v>
+        <v>480</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>162</v>
+        <v>482</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9681,19 +9706,19 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>441</v>
+        <v>478</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>83</v>
@@ -9705,7 +9730,7 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>137</v>
+        <v>483</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9716,10 +9741,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9727,7 +9752,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>94</v>
@@ -9739,23 +9764,19 @@
         <v>83</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>486</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>83</v>
       </c>
@@ -9779,11 +9800,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -9801,10 +9824,10 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
         <v>94</v>
@@ -9819,16 +9842,16 @@
         <v>83</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>503</v>
+        <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>298</v>
+        <v>456</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>299</v>
+        <v>487</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -9836,10 +9859,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9850,7 +9873,7 @@
         <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>83</v>
@@ -9862,20 +9885,18 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>358</v>
+        <v>489</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>505</v>
+        <v>490</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>506</v>
+        <v>490</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>491</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>83</v>
       </c>
@@ -9923,13 +9944,13 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>83</v>
@@ -9941,27 +9962,27 @@
         <v>83</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>508</v>
+        <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>364</v>
+        <v>492</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>365</v>
+        <v>493</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>366</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9972,7 +9993,7 @@
         <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>83</v>
@@ -9981,23 +10002,21 @@
         <v>83</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>201</v>
+        <v>495</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>510</v>
+        <v>496</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>83</v>
       </c>
@@ -10021,13 +10040,13 @@
         <v>83</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>373</v>
+        <v>83</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>83</v>
@@ -10045,16 +10064,16 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>374</v>
+        <v>83</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>106</v>
@@ -10066,10 +10085,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>137</v>
+        <v>492</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>375</v>
+        <v>498</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10080,14 +10099,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10103,22 +10122,22 @@
         <v>83</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>201</v>
+        <v>437</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10143,11 +10162,13 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="Y68" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z68" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -10165,7 +10186,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>513</v>
+        <v>499</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10183,27 +10204,27 @@
         <v>83</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>383</v>
+        <v>503</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>384</v>
+        <v>504</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>385</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10214,7 +10235,7 @@
         <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>83</v>
@@ -10226,20 +10247,16 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>84</v>
+        <v>209</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>519</v>
+        <v>210</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>83</v>
       </c>
@@ -10287,36 +10304,884 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="P71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="Y72" s="2"/>
+      <c r="Z72" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AG69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH69" t="s" s="2">
+      <c r="B74" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G75" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="AI69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
+      <c r="H75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="Y75" s="2"/>
+      <c r="Z75" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="AK69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP69" t="s" s="2">
+      <c r="AK75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2945" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="542">
   <si>
     <t>Property</t>
   </si>
@@ -926,67 +926,97 @@
     <t>心電図検査を示すコード</t>
   </si>
   <si>
+    <t>observationの意味を正しく理解するには、すべてのcode-valueペアと、さらに存在する場合にはcomponent.code-component.valueのペアが、考慮される必要がある。</t>
+  </si>
+  <si>
+    <t>どのような観察が行われているかを知ることは、観察を理解するために不可欠です。 / Knowing what kind of observation is being made is essential to understanding the observation.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS</t>
+  </si>
+  <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
+  </si>
+  <si>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:ekgCode</t>
+  </si>
+  <si>
+    <t>ekgCode</t>
+  </si>
+  <si>
     <t>心電図検査(EKG Study)を示すLOINCコード 11524-6 を固定値として指定する。</t>
   </si>
   <si>
-    <t>どのような観察が行われているかを知ることは、観察を理解するために不可欠です。 / Knowing what kind of observation is being made is essential to understanding the observation.</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS</t>
-  </si>
-  <si>
-    <t>Event.code</t>
-  </si>
-  <si>
-    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>116680003 |Is a|</t>
-  </si>
-  <si>
-    <t>Observation.code.id</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
+    <t>Observation.code.coding:ekgCode.id</t>
   </si>
   <si>
     <t>Observation.code.coding.id</t>
   </si>
   <si>
+    <t>Observation.code.coding:ekgCode.extension</t>
+  </si>
+  <si>
     <t>Observation.code.coding.extension</t>
   </si>
   <si>
+    <t>Observation.code.coding:ekgCode.system</t>
+  </si>
+  <si>
     <t>Observation.code.coding.system</t>
   </si>
   <si>
     <t>Loinc_CS</t>
   </si>
   <si>
+    <t>Observation.code.coding:ekgCode.version</t>
+  </si>
+  <si>
     <t>Observation.code.coding.version</t>
   </si>
   <si>
+    <t>Observation.code.coding:ekgCode.code</t>
+  </si>
+  <si>
     <t>Observation.code.coding.code</t>
   </si>
   <si>
     <t>11524-6</t>
   </si>
   <si>
+    <t>Observation.code.coding:ekgCode.display</t>
+  </si>
+  <si>
     <t>Observation.code.coding.display</t>
   </si>
   <si>
     <t>EKG Study</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:ekgCode.userSelected</t>
   </si>
   <si>
     <t>Observation.code.coding.userSelected</t>
@@ -1981,7 +2011,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP76"/>
+  <dimension ref="A1:AP77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.17578125" customWidth="true" bestFit="true"/>
@@ -5888,7 +5918,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>82</v>
@@ -5952,16 +5982,14 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="AC33" s="2"/>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>226</v>
@@ -6002,15 +6030,17 @@
         <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>306</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>94</v>
@@ -6022,19 +6052,23 @@
         <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>210</v>
+        <v>307</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
@@ -6082,19 +6116,19 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>83</v>
@@ -6103,10 +6137,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6117,21 +6151,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
@@ -6143,17 +6177,15 @@
         <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6190,31 +6222,31 @@
         <v>83</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>83</v>
@@ -6237,21 +6269,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6260,29 +6292,27 @@
         <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>308</v>
+        <v>83</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6312,31 +6342,31 @@
         <v>83</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>83</v>
@@ -6345,10 +6375,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>244</v>
+        <v>83</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6359,10 +6389,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6370,7 +6400,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>94</v>
@@ -6385,24 +6415,26 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>209</v>
+        <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>83</v>
+        <v>314</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>83</v>
@@ -6444,7 +6476,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6465,10 +6497,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6479,10 +6511,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6505,24 +6537,24 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>114</v>
+        <v>209</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>311</v>
+        <v>83</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>83</v>
@@ -6564,7 +6596,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6585,10 +6617,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6599,10 +6631,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6625,27 +6657,27 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>209</v>
+        <v>114</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>83</v>
+        <v>319</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>313</v>
+        <v>83</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>83</v>
@@ -6684,7 +6716,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6705,10 +6737,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6719,10 +6751,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6745,19 +6777,17 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>274</v>
+        <v>209</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6767,7 +6797,7 @@
         <v>83</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>83</v>
+        <v>322</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>83</v>
@@ -6806,7 +6836,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6827,10 +6857,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6841,10 +6871,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6867,19 +6897,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>209</v>
+        <v>274</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6928,7 +6958,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6949,10 +6979,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -6963,10 +6993,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6989,19 +7019,19 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>317</v>
+        <v>209</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>318</v>
+        <v>283</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>318</v>
+        <v>284</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>319</v>
+        <v>285</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>320</v>
+        <v>286</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7050,7 +7080,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>316</v>
+        <v>287</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7065,19 +7095,19 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>321</v>
+        <v>83</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>322</v>
+        <v>288</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>323</v>
+        <v>289</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>324</v>
+        <v>83</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>83</v>
@@ -7085,10 +7115,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7099,7 +7129,7 @@
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>83</v>
@@ -7111,18 +7141,20 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7170,13 +7202,13 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>83</v>
@@ -7185,19 +7217,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>83</v>
+        <v>331</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7205,21 +7237,21 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -7231,20 +7263,18 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7292,13 +7322,13 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
@@ -7307,19 +7337,19 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>336</v>
+        <v>83</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>337</v>
+        <v>298</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7456,7 +7486,7 @@
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>83</v>
+        <v>351</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7475,18 +7505,20 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7549,19 +7581,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>83</v>
+        <v>356</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7569,10 +7601,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7583,7 +7615,7 @@
         <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
@@ -7595,20 +7627,18 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>361</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7656,13 +7686,13 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
@@ -7671,19 +7701,19 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>362</v>
+        <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
@@ -7691,10 +7721,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7705,7 +7735,7 @@
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7717,19 +7747,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7778,25 +7808,25 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>371</v>
+        <v>83</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>83</v>
+        <v>372</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>372</v>
+        <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>373</v>
@@ -7805,10 +7835,10 @@
         <v>374</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>83</v>
+        <v>375</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>375</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49">
@@ -7836,22 +7866,22 @@
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>201</v>
+        <v>377</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7876,13 +7906,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7909,7 +7939,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -7918,10 +7948,10 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>83</v>
+        <v>382</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>137</v>
+        <v>383</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>384</v>
@@ -7930,26 +7960,26 @@
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>386</v>
+        <v>83</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -7998,11 +8028,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8020,16 +8052,16 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>83</v>
+        <v>393</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -8038,19 +8070,19 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>392</v>
+        <v>137</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>394</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51">
@@ -8062,7 +8094,7 @@
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8081,7 +8113,7 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>396</v>
+        <v>201</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>397</v>
@@ -8118,13 +8150,11 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8160,27 +8190,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>83</v>
+        <v>401</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>83</v>
+        <v>404</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8191,7 +8221,7 @@
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>83</v>
@@ -8203,18 +8233,20 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>201</v>
+        <v>406</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8238,37 +8270,37 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF52" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="Y52" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>83</v>
@@ -8280,19 +8312,19 @@
         <v>83</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>408</v>
+        <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>411</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53">
@@ -8334,9 +8366,7 @@
       <c r="N53" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="O53" t="s" s="2">
-        <v>415</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8360,7 +8390,7 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="Y53" t="s" s="2">
         <v>416</v>
@@ -8402,27 +8432,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>83</v>
+        <v>418</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>83</v>
+        <v>421</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8445,18 +8475,20 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>421</v>
+        <v>201</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>424</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
       </c>
@@ -8480,13 +8512,13 @@
         <v>83</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>83</v>
+        <v>415</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>83</v>
+        <v>426</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>83</v>
+        <v>427</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -8504,7 +8536,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8522,27 +8554,27 @@
         <v>83</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>424</v>
+        <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>427</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8565,16 +8597,16 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8624,7 +8656,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8642,27 +8674,27 @@
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8673,7 +8705,7 @@
         <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>83</v>
@@ -8685,20 +8717,18 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>441</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>83</v>
       </c>
@@ -8746,45 +8776,45 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>441</v>
+        <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>83</v>
+        <v>442</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>83</v>
+        <v>445</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8795,7 +8825,7 @@
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>83</v>
@@ -8807,16 +8837,20 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>209</v>
+        <v>447</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>210</v>
+        <v>448</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>448</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
       </c>
@@ -8864,19 +8898,19 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>212</v>
+        <v>446</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>83</v>
+        <v>451</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
@@ -8885,10 +8919,10 @@
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>83</v>
+        <v>452</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>213</v>
+        <v>453</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -8899,21 +8933,21 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>83</v>
@@ -8925,17 +8959,15 @@
         <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -8984,19 +9016,19 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>83</v>
@@ -9019,14 +9051,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>447</v>
+        <v>158</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9039,26 +9071,24 @@
         <v>83</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>448</v>
+        <v>215</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>449</v>
+        <v>216</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="O59" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9106,7 +9136,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>450</v>
+        <v>218</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9130,7 +9160,7 @@
         <v>83</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9141,42 +9171,46 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>83</v>
+        <v>457</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>452</v>
+        <v>139</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
@@ -9224,19 +9258,19 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>455</v>
+        <v>83</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>83</v>
@@ -9245,10 +9279,10 @@
         <v>83</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>456</v>
+        <v>83</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>457</v>
+        <v>137</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9259,10 +9293,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9285,13 +9319,13 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9342,7 +9376,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9351,7 +9385,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9363,10 +9397,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9377,10 +9411,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9403,20 +9437,16 @@
         <v>83</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>201</v>
+        <v>462</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9440,31 +9470,31 @@
         <v>83</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>467</v>
+        <v>83</v>
       </c>
       <c r="Z62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF62" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9473,7 +9503,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>83</v>
+        <v>465</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -9482,13 +9512,13 @@
         <v>83</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>469</v>
+        <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>393</v>
+        <v>471</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9499,10 +9529,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9513,7 +9543,7 @@
         <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>83</v>
@@ -9528,16 +9558,16 @@
         <v>201</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9562,13 +9592,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>405</v>
+        <v>118</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9586,13 +9616,13 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>83</v>
@@ -9604,13 +9634,13 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9621,10 +9651,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9635,7 +9665,7 @@
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>83</v>
@@ -9647,17 +9677,19 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>479</v>
+        <v>201</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N64" s="2"/>
+        <v>483</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>484</v>
+      </c>
       <c r="O64" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -9682,13 +9714,13 @@
         <v>83</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>83</v>
+        <v>415</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>83</v>
+        <v>486</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>83</v>
+        <v>487</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
@@ -9706,13 +9738,13 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>83</v>
@@ -9724,13 +9756,13 @@
         <v>83</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>83</v>
+        <v>479</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>83</v>
+        <v>480</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>483</v>
+        <v>403</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9741,10 +9773,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9767,16 +9799,18 @@
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>209</v>
+        <v>489</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
       </c>
@@ -9824,7 +9858,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9845,10 +9879,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>456</v>
+        <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9859,10 +9893,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9873,7 +9907,7 @@
         <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>83</v>
@@ -9882,20 +9916,18 @@
         <v>83</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>489</v>
+        <v>209</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -9944,13 +9976,13 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>83</v>
@@ -9965,10 +9997,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>492</v>
+        <v>466</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -9979,10 +10011,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10005,16 +10037,16 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10064,7 +10096,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10085,10 +10117,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>492</v>
+        <v>502</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10099,10 +10131,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10125,20 +10157,18 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>437</v>
+        <v>505</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>507</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>83</v>
       </c>
@@ -10186,7 +10216,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10207,10 +10237,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10221,10 +10251,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10235,7 +10265,7 @@
         <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>83</v>
@@ -10244,19 +10274,23 @@
         <v>83</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>209</v>
+        <v>447</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>210</v>
+        <v>510</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>510</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
       </c>
@@ -10304,19 +10338,19 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>212</v>
+        <v>509</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>83</v>
@@ -10325,10 +10359,10 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>83</v>
+        <v>513</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>213</v>
+        <v>514</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10339,21 +10373,21 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>83</v>
@@ -10365,17 +10399,15 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>139</v>
+        <v>209</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10424,19 +10456,19 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>83</v>
@@ -10459,14 +10491,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>447</v>
+        <v>158</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10479,26 +10511,24 @@
         <v>83</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
         <v>139</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>448</v>
+        <v>215</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>449</v>
+        <v>216</v>
       </c>
       <c r="N71" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="O71" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10546,7 +10576,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>450</v>
+        <v>218</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10570,7 +10600,7 @@
         <v>83</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10581,45 +10611,45 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>83</v>
+        <v>457</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J72" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>509</v>
+        <v>458</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>510</v>
+        <v>459</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>511</v>
+        <v>161</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>294</v>
+        <v>162</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>83</v>
@@ -10644,11 +10674,13 @@
         <v>83</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>83</v>
@@ -10666,34 +10698,34 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>508</v>
+        <v>460</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>512</v>
+        <v>83</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>299</v>
+        <v>137</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>83</v>
@@ -10701,10 +10733,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10712,7 +10744,7 @@
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G73" t="s" s="2">
         <v>94</v>
@@ -10727,19 +10759,19 @@
         <v>95</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>367</v>
+        <v>201</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>370</v>
+        <v>294</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -10764,13 +10796,11 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y73" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10788,10 +10818,10 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH73" t="s" s="2">
         <v>94</v>
@@ -10806,27 +10836,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>373</v>
+        <v>298</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>374</v>
+        <v>299</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>83</v>
+        <v>300</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>375</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10846,22 +10876,22 @@
         <v>83</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>201</v>
+        <v>377</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10886,13 +10916,13 @@
         <v>83</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>380</v>
+        <v>83</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>83</v>
@@ -10910,7 +10940,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10919,7 +10949,7 @@
         <v>94</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>106</v>
@@ -10928,10 +10958,10 @@
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>83</v>
+        <v>527</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>137</v>
+        <v>383</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>384</v>
@@ -10940,26 +10970,26 @@
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>386</v>
+        <v>83</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>83</v>
@@ -10974,16 +11004,16 @@
         <v>201</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>526</v>
+        <v>389</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11008,11 +11038,13 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="Y75" s="2"/>
+        <v>390</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>391</v>
+      </c>
       <c r="Z75" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11030,16 +11062,16 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>83</v>
+        <v>393</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>106</v>
@@ -11048,31 +11080,31 @@
         <v>83</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>392</v>
+        <v>137</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>394</v>
+        <v>83</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11091,19 +11123,19 @@
         <v>83</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>84</v>
+        <v>201</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11128,13 +11160,11 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11152,7 +11182,7 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11170,18 +11200,140 @@
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>83</v>
+        <v>401</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>442</v>
+        <v>402</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>443</v>
+        <v>403</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -989,7 +989,7 @@
     <t>Observation.code.coding.system</t>
   </si>
   <si>
-    <t>Loinc_CS</t>
+    <t>http://loinc.org</t>
   </si>
   <si>
     <t>Observation.code.coding:ekgCode.version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2984" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3061" uniqueCount="546">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-07</t>
+    <t>2024-11-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -502,6 +502,38 @@
   </si>
   <si>
     <t>心電図検査の所見が機械的に判定されたものであるかどうかを示す</t>
+  </si>
+  <si>
+    <t>Observation.extension:duration</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_Duration}
+</t>
+  </si>
+  <si>
+    <t>測定を行った時間(長さ)</t>
+  </si>
+  <si>
+    <t>心電図検査で測定が行われた時間を示す。</t>
+  </si>
+  <si>
+    <t>Observation.extension:stressType</t>
+  </si>
+  <si>
+    <t>stressType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_Observation_Electrocardiogram_StressType}
+</t>
+  </si>
+  <si>
+    <t>負荷心電図種別</t>
+  </si>
+  <si>
+    <t>負荷心電図の種別を示す拡張である。</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -648,7 +680,7 @@
 </t>
   </si>
   <si>
-    <t>Observationリソースに対する分類コード。心電図検査には procedure が指定される。</t>
+    <t>Observationリソースに対する分類コード。心電図検査には通常 procedure が指定される。必要に応じてextraCategoryを仕様する</t>
   </si>
   <si>
     <t>階層的にカテゴリーを設定することで粒度のレベルを概念定義できる。</t>
@@ -713,7 +745,7 @@
     <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
   </si>
   <si>
-    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+    <t>心電図検査は通常 procedure に分類される。</t>
   </si>
   <si>
     <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
@@ -732,28 +764,28 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Observation.category.coding:simpleCategory</t>
-  </si>
-  <si>
-    <t>simpleCategory</t>
-  </si>
-  <si>
-    <t>心電図検査は procedure に分類されている。</t>
-  </si>
-  <si>
-    <t>Observation.category.coding:simpleCategory.id</t>
+    <t>Observation.category.coding:electrocardiogram</t>
+  </si>
+  <si>
+    <t>electrocardiogram</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:electrocardiogram.id</t>
   </si>
   <si>
     <t>Observation.category.coding.id</t>
   </si>
   <si>
-    <t>Observation.category.coding:simpleCategory.extension</t>
+    <t>Observation.category.coding:electrocardiogram.extension</t>
   </si>
   <si>
     <t>Observation.category.coding.extension</t>
   </si>
   <si>
-    <t>Observation.category.coding:simpleCategory.system</t>
+    <t>Observation.category.coding:electrocardiogram.system</t>
   </si>
   <si>
     <t>Observation.category.coding.system</t>
@@ -783,7 +815,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>Observation.category.coding:simpleCategory.version</t>
+    <t>Observation.category.coding:electrocardiogram.version</t>
   </si>
   <si>
     <t>Observation.category.coding.version</t>
@@ -807,7 +839,7 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>Observation.category.coding:simpleCategory.code</t>
+    <t>Observation.category.coding:electrocardiogram.code</t>
   </si>
   <si>
     <t>Observation.category.coding.code</t>
@@ -834,7 +866,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Observation.category.coding:simpleCategory.display</t>
+    <t>Observation.category.coding:electrocardiogram.display</t>
   </si>
   <si>
     <t>Observation.category.coding.display</t>
@@ -849,9 +881,6 @@
     <t>システムを知らない読者のために、コードの人間の読み取り可能な意味を持ち込むことができる必要があります。 / Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
   </si>
   <si>
-    <t>Procedure</t>
-  </si>
-  <si>
     <t>Coding.display</t>
   </si>
   <si>
@@ -861,7 +890,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Observation.category.coding:simpleCategory.userSelected</t>
+    <t>Observation.category.coding:electrocardiogram.userSelected</t>
   </si>
   <si>
     <t>Observation.category.coding.userSelected</t>
@@ -892,6 +921,45 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
+    <t>Observation.category.coding:extraCategory</t>
+  </si>
+  <si>
+    <t>extraCategory</t>
+  </si>
+  <si>
+    <t>心電図検査について、負荷試験などの条件をつけた分類</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramExtraCategory_VS</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:extraCategory.id</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:extraCategory.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:extraCategory.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationElectrocardiogramExtraCategory_CS</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:extraCategory.version</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:extraCategory.code</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:extraCategory.display</t>
+  </si>
+  <si>
+    <t>Observation.category.coding:extraCategory.userSelected</t>
+  </si>
+  <si>
     <t>Observation.category.text</t>
   </si>
   <si>
@@ -926,13 +994,16 @@
     <t>心電図検査を示すコード</t>
   </si>
   <si>
-    <t>observationの意味を正しく理解するには、すべてのcode-valueペアと、さらに存在する場合にはcomponent.code-component.valueのペアが、考慮される必要がある。</t>
+    <t>心電図検査(LOINC: EKG Study)を示すLOINCコード 11524-6 を固定値として指定する。</t>
   </si>
   <si>
     <t>どのような観察が行われているかを知ることは、観察を理解するために不可欠です。 / Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS</t>
+    <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -962,64 +1033,11 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t>Observation.code.coding:ekgCode</t>
-  </si>
-  <si>
-    <t>ekgCode</t>
-  </si>
-  <si>
-    <t>心電図検査(EKG Study)を示すLOINCコード 11524-6 を固定値として指定する。</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:ekgCode.id</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:ekgCode.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:ekgCode.system</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:ekgCode.version</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:ekgCode.code</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.code</t>
-  </si>
-  <si>
-    <t>11524-6</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:ekgCode.display</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.display</t>
-  </si>
-  <si>
-    <t>EKG Study</t>
-  </si>
-  <si>
-    <t>Observation.code.coding:ekgCode.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.userSelected</t>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://loinc.org"/&gt;
+  &lt;code value="11524-6"/&gt;
+  &lt;display value="EKG Study"/&gt;
+&lt;/valueCoding&gt;</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -1306,9 +1324,6 @@
     <t>観察結果で見つかったコードで暗黙的ではない場合にのみ使用されます。多くのシステムでは、これはインラインコンポーネントの代わりに関連する観察として表される場合があります。
 ユースケースでは、ボディサイトを個別のリソースとして処理する必要がある場合（たとえば、個別に識別および追跡するため）、標準の拡張[BodySite]（Extension-BodySite.html）を使用します。 / Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>example</t>
   </si>
   <si>
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
@@ -1645,6 +1660,9 @@
   </si>
   <si>
     <t>心電図の各検査項目についてはLOINCなどの特定の用語集を利用することが推奨される。</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramComponentCode_VS</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR @@ -2011,10 +2029,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP77"/>
+  <dimension ref="A1:AP79"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.17578125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="19.76953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -3384,43 +3402,41 @@
         <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="D12" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>83</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N12" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="O12" t="s" s="2">
-        <v>162</v>
-      </c>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>83</v>
       </c>
@@ -3468,7 +3484,7 @@
         <v>83</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3477,7 +3493,7 @@
         <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>145</v>
@@ -3492,7 +3508,7 @@
         <v>83</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>83</v>
@@ -3503,12 +3519,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>83</v>
       </c>
@@ -3517,7 +3535,7 @@
         <v>81</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>83</v>
@@ -3526,21 +3544,19 @@
         <v>83</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
         <v>166</v>
       </c>
       <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
-        <v>167</v>
-      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>83</v>
       </c>
@@ -3588,7 +3604,7 @@
         <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3597,25 +3613,25 @@
         <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>169</v>
+        <v>83</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>170</v>
+        <v>83</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>171</v>
+        <v>83</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>83</v>
@@ -3623,14 +3639,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3643,23 +3659,25 @@
         <v>83</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>174</v>
+        <v>139</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N14" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N14" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O14" t="s" s="2">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>83</v>
@@ -3708,7 +3726,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3720,19 +3738,19 @@
         <v>83</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>178</v>
+        <v>83</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>83</v>
@@ -3743,14 +3761,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>181</v>
+        <v>83</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3769,18 +3787,18 @@
         <v>95</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O15" s="2"/>
+        <v>176</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>83</v>
       </c>
@@ -3828,7 +3846,7 @@
         <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3843,19 +3861,19 @@
         <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>83</v>
+        <v>181</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3863,45 +3881,43 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>83</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -3926,13 +3942,13 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>192</v>
+        <v>83</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>193</v>
+        <v>83</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>194</v>
+        <v>83</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3950,13 +3966,13 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>83</v>
@@ -3965,19 +3981,19 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>196</v>
+        <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>199</v>
+        <v>83</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>83</v>
@@ -3985,14 +4001,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>83</v>
+        <v>191</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4008,23 +4024,21 @@
         <v>83</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>83</v>
       </c>
@@ -4048,11 +4062,13 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y17" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z17" t="s" s="2">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -4070,7 +4086,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4085,19 +4101,19 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>83</v>
+        <v>196</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>207</v>
+        <v>83</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>83</v>
@@ -4105,10 +4121,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4116,7 +4132,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>94</v>
@@ -4125,22 +4141,26 @@
         <v>83</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>209</v>
+        <v>114</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>83</v>
       </c>
@@ -4164,13 +4184,13 @@
         <v>83</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>83</v>
+        <v>202</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>83</v>
+        <v>203</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>83</v>
@@ -4188,10 +4208,10 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>94</v>
@@ -4200,22 +4220,22 @@
         <v>83</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -4223,14 +4243,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4249,18 +4269,20 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>139</v>
+        <v>211</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O19" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="O19" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P19" t="s" s="2">
         <v>83</v>
       </c>
@@ -4284,31 +4306,29 @@
         <v>83</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4320,7 +4340,7 @@
         <v>83</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>83</v>
@@ -4332,10 +4352,10 @@
         <v>83</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -4343,10 +4363,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4357,7 +4377,7 @@
         <v>81</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>83</v>
@@ -4366,23 +4386,19 @@
         <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>224</v>
-      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>83</v>
       </c>
@@ -4418,29 +4434,31 @@
         <v>83</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AC20" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>83</v>
@@ -4449,10 +4467,10 @@
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>227</v>
+        <v>83</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>83</v>
@@ -4463,23 +4481,21 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>83</v>
@@ -4488,23 +4504,21 @@
         <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>83</v>
       </c>
@@ -4528,29 +4542,31 @@
         <v>83</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="Y21" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z21" t="s" s="2">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4562,7 +4578,7 @@
         <v>83</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>83</v>
@@ -4571,10 +4587,10 @@
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>227</v>
+        <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4585,10 +4601,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4596,10 +4612,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>83</v>
@@ -4608,19 +4624,23 @@
         <v>83</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
@@ -4656,31 +4676,29 @@
         <v>83</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="AC22" s="2"/>
       <c r="AD22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>83</v>
@@ -4689,10 +4707,10 @@
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>83</v>
+        <v>237</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -4703,21 +4721,23 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="D23" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>83</v>
@@ -4726,21 +4746,23 @@
         <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>139</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>241</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
       </c>
@@ -4764,31 +4786,29 @@
         <v>83</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AD23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4800,7 +4820,7 @@
         <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>83</v>
@@ -4809,10 +4829,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>83</v>
+        <v>237</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -4823,10 +4843,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4834,7 +4854,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>94</v>
@@ -4846,29 +4866,25 @@
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>242</v>
+        <v>83</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>83</v>
@@ -4910,7 +4926,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4922,7 +4938,7 @@
         <v>83</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>83</v>
@@ -4931,10 +4947,10 @@
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>244</v>
+        <v>83</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -4945,21 +4961,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>83</v>
@@ -4968,19 +4984,19 @@
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>250</v>
+        <v>171</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5018,31 +5034,31 @@
         <v>83</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>83</v>
@@ -5051,10 +5067,10 @@
         <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>252</v>
+        <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5065,10 +5081,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5076,7 +5092,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>94</v>
@@ -5091,24 +5107,26 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>249</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>83</v>
@@ -5150,7 +5168,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5171,10 +5189,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5185,10 +5203,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5211,24 +5229,24 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>268</v>
+        <v>83</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>83</v>
@@ -5270,7 +5288,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5291,10 +5309,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5305,10 +5323,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5331,26 +5349,24 @@
         <v>95</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>274</v>
+        <v>114</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>83</v>
+        <v>269</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>83</v>
@@ -5392,7 +5408,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5413,10 +5429,10 @@
         <v>83</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
@@ -5427,10 +5443,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5453,19 +5469,17 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
@@ -5514,7 +5528,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5535,10 +5549,10 @@
         <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
@@ -5549,18 +5563,18 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>94</v>
@@ -5575,19 +5589,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>201</v>
+        <v>283</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -5612,11 +5626,13 @@
         <v>83</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y30" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>83</v>
@@ -5634,10 +5650,10 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>94</v>
@@ -5649,32 +5665,34 @@
         <v>106</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>296</v>
+        <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>297</v>
+        <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="C31" s="2"/>
+        <v>229</v>
+      </c>
+      <c r="C31" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="D31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5692,19 +5710,23 @@
         <v>83</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5728,13 +5750,11 @@
         <v>83</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>83</v>
+        <v>295</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>83</v>
@@ -5752,19 +5772,19 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>83</v>
@@ -5773,10 +5793,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>83</v>
+        <v>237</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -5787,21 +5807,21 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>303</v>
+        <v>243</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>83</v>
@@ -5813,17 +5833,15 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>83</v>
@@ -5860,31 +5878,31 @@
         <v>83</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>83</v>
@@ -5896,7 +5914,7 @@
         <v>83</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5907,18 +5925,18 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>245</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>82</v>
@@ -5930,23 +5948,21 @@
         <v>83</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>220</v>
+        <v>139</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>224</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
@@ -5982,9 +5998,11 @@
         <v>83</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>83</v>
       </c>
@@ -5992,7 +6010,7 @@
         <v>143</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6004,7 +6022,7 @@
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -6013,10 +6031,10 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>227</v>
+        <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6027,14 +6045,12 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>83</v>
       </c>
@@ -6055,19 +6071,19 @@
         <v>95</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>220</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>248</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>307</v>
+        <v>250</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6077,7 +6093,7 @@
         <v>83</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>83</v>
@@ -6116,13 +6132,13 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>83</v>
@@ -6137,10 +6153,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6151,10 +6167,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>309</v>
+        <v>257</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6174,18 +6190,20 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>210</v>
+        <v>258</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
@@ -6234,7 +6252,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>212</v>
+        <v>261</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6246,7 +6264,7 @@
         <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>83</v>
@@ -6255,10 +6273,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>83</v>
+        <v>262</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>213</v>
+        <v>263</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6269,21 +6287,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6292,21 +6310,21 @@
         <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>215</v>
+        <v>266</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
@@ -6342,31 +6360,31 @@
         <v>83</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>217</v>
+        <v>83</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>218</v>
+        <v>270</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>83</v>
@@ -6375,10 +6393,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>83</v>
+        <v>271</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>213</v>
+        <v>272</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6389,10 +6407,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>313</v>
+        <v>274</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6400,7 +6418,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>94</v>
@@ -6415,26 +6433,24 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>238</v>
+        <v>275</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>240</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>241</v>
+        <v>277</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>314</v>
+        <v>83</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>83</v>
@@ -6476,7 +6492,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6497,10 +6513,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>244</v>
+        <v>279</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>245</v>
+        <v>280</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6511,10 +6527,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>316</v>
+        <v>282</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6537,18 +6553,20 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>209</v>
+        <v>283</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>248</v>
+        <v>284</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>249</v>
+        <v>285</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>287</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -6596,7 +6614,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>251</v>
+        <v>288</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6617,10 +6635,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>253</v>
+        <v>290</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6631,10 +6649,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6657,24 +6675,26 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>114</v>
+        <v>219</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>256</v>
+        <v>305</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>258</v>
+        <v>308</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>83</v>
@@ -6716,7 +6736,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>260</v>
+        <v>309</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6737,10 +6757,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>261</v>
+        <v>310</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>262</v>
+        <v>311</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6751,18 +6771,18 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>83</v>
+        <v>313</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>94</v>
@@ -6777,17 +6797,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>265</v>
+        <v>314</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>267</v>
+        <v>316</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -6797,7 +6819,7 @@
         <v>83</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>322</v>
+        <v>83</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>83</v>
@@ -6812,13 +6834,13 @@
         <v>83</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>83</v>
+        <v>317</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>83</v>
+        <v>318</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -6836,10 +6858,10 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>269</v>
+        <v>312</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>94</v>
@@ -6851,30 +6873,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>83</v>
+        <v>319</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>83</v>
+        <v>320</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>270</v>
+        <v>321</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>271</v>
+        <v>322</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6894,23 +6916,19 @@
         <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>274</v>
+        <v>219</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>275</v>
+        <v>220</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
       </c>
@@ -6958,7 +6976,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>279</v>
+        <v>222</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6970,7 +6988,7 @@
         <v>83</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>83</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>83</v>
@@ -6979,10 +6997,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>280</v>
+        <v>83</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>281</v>
+        <v>223</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -6993,21 +7011,21 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>83</v>
@@ -7016,23 +7034,21 @@
         <v>83</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>209</v>
+        <v>139</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>283</v>
+        <v>225</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>284</v>
+        <v>226</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>286</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>83</v>
       </c>
@@ -7068,31 +7084,31 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>83</v>
+        <v>227</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>287</v>
+        <v>228</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>83</v>
@@ -7101,10 +7117,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>289</v>
+        <v>223</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7115,10 +7131,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7129,7 +7145,7 @@
         <v>81</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>83</v>
@@ -7141,26 +7157,26 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>327</v>
+        <v>230</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>328</v>
+        <v>231</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>328</v>
+        <v>232</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>329</v>
+        <v>241</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>330</v>
+        <v>234</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>83</v>
+        <v>328</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>83</v>
@@ -7202,13 +7218,13 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>236</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>83</v>
@@ -7217,19 +7233,19 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>331</v>
+        <v>83</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>332</v>
+        <v>237</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>333</v>
+        <v>238</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>334</v>
+        <v>83</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>83</v>
@@ -7237,10 +7253,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7251,7 +7267,7 @@
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -7263,18 +7279,20 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>336</v>
+        <v>219</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>337</v>
+        <v>305</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>337</v>
+        <v>306</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7322,13 +7340,13 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>335</v>
+        <v>309</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
@@ -7343,13 +7361,13 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>339</v>
+        <v>311</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>334</v>
+        <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -7357,14 +7375,14 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>341</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7383,19 +7401,19 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7444,7 +7462,7 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7459,19 +7477,19 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>83</v>
@@ -7479,21 +7497,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>351</v>
+        <v>83</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>83</v>
@@ -7505,20 +7523,18 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7566,13 +7582,13 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>83</v>
@@ -7581,19 +7597,19 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>356</v>
+        <v>83</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>357</v>
+        <v>321</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>359</v>
+        <v>338</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>83</v>
@@ -7601,14 +7617,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>83</v>
+        <v>345</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7627,18 +7643,20 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
       </c>
@@ -7686,7 +7704,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7701,19 +7719,19 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>83</v>
+        <v>350</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
@@ -7721,21 +7739,21 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>83</v>
+        <v>355</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>83</v>
@@ -7747,19 +7765,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7808,13 +7826,13 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>83</v>
@@ -7823,19 +7841,19 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>83</v>
@@ -7843,10 +7861,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7869,20 +7887,18 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>380</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>83</v>
       </c>
@@ -7930,7 +7946,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7939,7 +7955,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>381</v>
+        <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -7948,27 +7964,27 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>382</v>
+        <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>83</v>
+        <v>370</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>385</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7979,7 +7995,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -7988,22 +8004,22 @@
         <v>83</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>201</v>
+        <v>372</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>387</v>
+        <v>373</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>388</v>
+        <v>374</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8028,13 +8044,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>392</v>
+        <v>83</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -8052,34 +8068,34 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>393</v>
+        <v>83</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>83</v>
+        <v>376</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>137</v>
+        <v>377</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>83</v>
@@ -8087,21 +8103,21 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>83</v>
@@ -8110,22 +8126,22 @@
         <v>83</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>201</v>
+        <v>381</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8150,11 +8166,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>400</v>
+        <v>83</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8172,16 +8190,16 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>83</v>
+        <v>385</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>106</v>
@@ -8190,27 +8208,27 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>404</v>
+        <v>389</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8221,7 +8239,7 @@
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>83</v>
@@ -8233,19 +8251,19 @@
         <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>406</v>
+        <v>211</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>408</v>
+        <v>392</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>409</v>
+        <v>393</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8270,13 +8288,13 @@
         <v>83</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>83</v>
+        <v>395</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>83</v>
@@ -8294,16 +8312,16 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>83</v>
+        <v>397</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8315,10 +8333,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>410</v>
+        <v>137</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8329,21 +8347,21 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>83</v>
+        <v>400</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>83</v>
@@ -8355,18 +8373,20 @@
         <v>83</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>403</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8390,13 +8410,11 @@
         <v>83</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>83</v>
@@ -8414,13 +8432,13 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>83</v>
@@ -8432,27 +8450,27 @@
         <v>83</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>421</v>
+        <v>408</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8463,7 +8481,7 @@
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8475,19 +8493,19 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>201</v>
+        <v>410</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>423</v>
+        <v>411</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8512,13 +8530,13 @@
         <v>83</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>426</v>
+        <v>83</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>427</v>
+        <v>83</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>83</v>
@@ -8536,13 +8554,13 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>83</v>
@@ -8557,10 +8575,10 @@
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8571,10 +8589,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8597,16 +8615,16 @@
         <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>431</v>
+        <v>211</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8632,13 +8650,13 @@
         <v>83</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>83</v>
+        <v>419</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>83</v>
+        <v>420</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>83</v>
@@ -8656,7 +8674,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8674,27 +8692,27 @@
         <v>83</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>437</v>
+        <v>424</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8717,18 +8735,20 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>439</v>
+        <v>211</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
       </c>
@@ -8752,13 +8772,13 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>83</v>
+        <v>429</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>83</v>
+        <v>430</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8776,7 +8796,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8794,27 +8814,27 @@
         <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>442</v>
+        <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>445</v>
+        <v>83</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8825,7 +8845,7 @@
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>83</v>
@@ -8837,20 +8857,18 @@
         <v>83</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>83</v>
       </c>
@@ -8898,45 +8916,45 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>451</v>
+        <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>83</v>
+        <v>437</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>452</v>
+        <v>438</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>453</v>
+        <v>439</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>83</v>
+        <v>440</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8959,15 +8977,17 @@
         <v>83</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>209</v>
+        <v>442</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>210</v>
+        <v>443</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9016,7 +9036,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>212</v>
+        <v>441</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9028,37 +9048,37 @@
         <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>83</v>
+        <v>445</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>83</v>
+        <v>446</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>213</v>
+        <v>447</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>83</v>
+        <v>448</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9077,18 +9097,20 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>139</v>
+        <v>450</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>215</v>
+        <v>451</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>216</v>
+        <v>451</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
       </c>
@@ -9136,7 +9158,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>218</v>
+        <v>449</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9148,7 +9170,7 @@
         <v>83</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>145</v>
+        <v>454</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>83</v>
@@ -9157,10 +9179,10 @@
         <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>83</v>
+        <v>455</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>213</v>
+        <v>456</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9171,46 +9193,42 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>457</v>
+        <v>83</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>458</v>
+        <v>220</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>83</v>
       </c>
@@ -9258,19 +9276,19 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>460</v>
+        <v>222</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>83</v>
@@ -9282,7 +9300,7 @@
         <v>83</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9293,21 +9311,21 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>83</v>
@@ -9319,15 +9337,17 @@
         <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>462</v>
+        <v>139</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>463</v>
+        <v>225</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9376,19 +9396,19 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>461</v>
+        <v>228</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>465</v>
+        <v>83</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>83</v>
@@ -9397,10 +9417,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>466</v>
+        <v>83</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>467</v>
+        <v>223</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9411,42 +9431,46 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>83</v>
+        <v>460</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="L62" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="N62" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9494,19 +9518,19 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>465</v>
+        <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>83</v>
@@ -9515,10 +9539,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>466</v>
+        <v>83</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>471</v>
+        <v>137</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9529,10 +9553,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9555,20 +9579,16 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>201</v>
+        <v>465</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>476</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>83</v>
       </c>
@@ -9592,13 +9612,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>477</v>
+        <v>83</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>478</v>
+        <v>83</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -9616,7 +9636,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9625,7 +9645,7 @@
         <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>83</v>
+        <v>468</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>106</v>
@@ -9634,13 +9654,13 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>479</v>
+        <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>403</v>
+        <v>470</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9651,10 +9671,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9665,7 +9685,7 @@
         <v>81</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>83</v>
@@ -9677,20 +9697,16 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>201</v>
+        <v>465</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
@@ -9714,13 +9730,13 @@
         <v>83</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>486</v>
+        <v>83</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>487</v>
+        <v>83</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>83</v>
@@ -9738,16 +9754,16 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>83</v>
+        <v>468</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>106</v>
@@ -9756,13 +9772,13 @@
         <v>83</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>479</v>
+        <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>403</v>
+        <v>474</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9773,10 +9789,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9799,17 +9815,19 @@
         <v>83</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>489</v>
+        <v>211</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>477</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="O65" t="s" s="2">
-        <v>492</v>
+        <v>479</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -9834,13 +9852,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>83</v>
+        <v>480</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>83</v>
+        <v>481</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -9858,7 +9876,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>488</v>
+        <v>475</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9876,13 +9894,13 @@
         <v>83</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>83</v>
+        <v>482</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>83</v>
+        <v>483</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>493</v>
+        <v>407</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -9893,10 +9911,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9907,7 +9925,7 @@
         <v>81</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>83</v>
@@ -9919,16 +9937,20 @@
         <v>83</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
       </c>
@@ -9952,13 +9974,13 @@
         <v>83</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>83</v>
+        <v>294</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>83</v>
+        <v>489</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>83</v>
+        <v>490</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>83</v>
@@ -9976,13 +9998,13 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>83</v>
@@ -9994,13 +10016,13 @@
         <v>83</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>83</v>
+        <v>482</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>497</v>
+        <v>407</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10011,10 +10033,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10025,7 +10047,7 @@
         <v>81</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>83</v>
@@ -10034,21 +10056,21 @@
         <v>83</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>500</v>
+        <v>493</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O67" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" t="s" s="2">
+        <v>495</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
       </c>
@@ -10096,13 +10118,13 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>83</v>
@@ -10117,10 +10139,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>502</v>
+        <v>83</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10131,10 +10153,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10145,7 +10167,7 @@
         <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>83</v>
@@ -10154,20 +10176,18 @@
         <v>83</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>505</v>
+        <v>219</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>507</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10216,13 +10236,13 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>83</v>
@@ -10237,10 +10257,10 @@
         <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>502</v>
+        <v>469</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10251,10 +10271,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10277,20 +10297,18 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>447</v>
+        <v>502</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>512</v>
-      </c>
+        <v>504</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>83</v>
       </c>
@@ -10338,7 +10356,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10359,10 +10377,10 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10373,10 +10391,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10387,7 +10405,7 @@
         <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>83</v>
@@ -10396,18 +10414,20 @@
         <v>83</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>209</v>
+        <v>508</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>210</v>
+        <v>509</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -10456,19 +10476,19 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>212</v>
+        <v>507</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>83</v>
@@ -10477,10 +10497,10 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>83</v>
+        <v>505</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>213</v>
+        <v>511</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -10491,14 +10511,14 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10514,21 +10534,23 @@
         <v>83</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>139</v>
+        <v>450</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>215</v>
+        <v>513</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>216</v>
+        <v>513</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>514</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>515</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
       </c>
@@ -10576,7 +10598,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>218</v>
+        <v>512</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10588,7 +10610,7 @@
         <v>83</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>83</v>
@@ -10597,10 +10619,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>83</v>
+        <v>516</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>213</v>
+        <v>517</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -10611,46 +10633,42 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>457</v>
+        <v>83</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>139</v>
+        <v>219</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>458</v>
+        <v>220</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>83</v>
       </c>
@@ -10698,19 +10716,19 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>460</v>
+        <v>222</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>83</v>
@@ -10722,7 +10740,7 @@
         <v>83</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>137</v>
+        <v>223</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -10733,21 +10751,21 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>83</v>
@@ -10756,23 +10774,21 @@
         <v>83</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>201</v>
+        <v>139</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>519</v>
+        <v>225</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>520</v>
+        <v>226</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>83</v>
       </c>
@@ -10796,11 +10812,13 @@
         <v>83</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>295</v>
+        <v>83</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>83</v>
@@ -10818,34 +10836,34 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>518</v>
+        <v>228</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>522</v>
+        <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>298</v>
+        <v>83</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>299</v>
+        <v>223</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>300</v>
+        <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>83</v>
@@ -10853,45 +10871,45 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>83</v>
+        <v>460</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>377</v>
+        <v>139</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>524</v>
+        <v>461</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>525</v>
+        <v>462</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>526</v>
+        <v>171</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>380</v>
+        <v>172</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -10940,45 +10958,45 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>523</v>
+        <v>463</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>527</v>
+        <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>383</v>
+        <v>83</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>384</v>
+        <v>137</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>385</v>
+        <v>83</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10986,7 +11004,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>94</v>
@@ -10998,22 +11016,22 @@
         <v>83</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>389</v>
+        <v>316</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11038,13 +11056,11 @@
         <v>83</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>392</v>
+        <v>525</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>83</v>
@@ -11062,16 +11078,16 @@
         <v>83</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>393</v>
+        <v>83</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>106</v>
@@ -11080,16 +11096,16 @@
         <v>83</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>83</v>
+        <v>526</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>137</v>
+        <v>321</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>394</v>
+        <v>322</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>83</v>
@@ -11097,21 +11113,21 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>83</v>
@@ -11120,22 +11136,22 @@
         <v>83</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>201</v>
+        <v>381</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>536</v>
+        <v>384</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>83</v>
@@ -11160,11 +11176,13 @@
         <v>83</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="Y76" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z76" t="s" s="2">
-        <v>400</v>
+        <v>83</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>83</v>
@@ -11182,13 +11200,13 @@
         <v>83</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>83</v>
@@ -11200,27 +11218,27 @@
         <v>83</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>401</v>
+        <v>531</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>404</v>
+        <v>389</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11231,7 +11249,7 @@
         <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>83</v>
@@ -11243,19 +11261,19 @@
         <v>83</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>84</v>
+        <v>211</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>541</v>
+        <v>393</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11280,13 +11298,13 @@
         <v>83</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>83</v>
+        <v>394</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>83</v>
+        <v>395</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>83</v>
@@ -11304,16 +11322,16 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>83</v>
+        <v>397</v>
       </c>
       <c r="AJ77" t="s" s="2">
         <v>106</v>
@@ -11325,15 +11343,257 @@
         <v>83</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>452</v>
+        <v>137</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>453</v>
+        <v>398</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP77" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="Y78" s="2"/>
+      <c r="Z78" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP79" t="s" s="2">
         <v>83</v>
       </c>
     </row>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidまたはmeta.lastupdatedを持たないものとします / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -329,16 +329,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -464,7 +464,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -1811,7 +1811,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9042" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9041" uniqueCount="760">
   <si>
     <t>Property</t>
   </si>
@@ -1718,10 +1718,7 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -19437,11 +19434,9 @@
       <c r="X139" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="Y139" t="s" s="2">
+      <c r="Y139" s="2"/>
+      <c r="Z139" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>83</v>
@@ -19477,27 +19472,27 @@
         <v>83</v>
       </c>
       <c r="AL139" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AM139" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="AM139" t="s" s="2">
+      <c r="AN139" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="AN139" t="s" s="2">
+      <c r="AO139" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP139" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP139" t="s" s="2">
-        <v>554</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19523,16 +19518,16 @@
         <v>211</v>
       </c>
       <c r="L140" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N140" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="M140" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N140" t="s" s="2">
+      <c r="O140" t="s" s="2">
         <v>557</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>558</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>83</v>
@@ -19560,11 +19555,11 @@
         <v>346</v>
       </c>
       <c r="Y140" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="Z140" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="Z140" t="s" s="2">
-        <v>560</v>
-      </c>
       <c r="AA140" t="s" s="2">
         <v>83</v>
       </c>
@@ -19581,7 +19576,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -19602,10 +19597,10 @@
         <v>83</v>
       </c>
       <c r="AM140" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AN140" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>83</v>
@@ -19616,10 +19611,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19642,16 +19637,16 @@
         <v>83</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="L141" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="M141" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N141" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19701,7 +19696,7 @@
         <v>83</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -19719,27 +19714,27 @@
         <v>83</v>
       </c>
       <c r="AL141" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AM141" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="AM141" t="s" s="2">
+      <c r="AN141" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="AN141" t="s" s="2">
+      <c r="AO141" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP141" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="AO141" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP141" t="s" s="2">
-        <v>570</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19762,16 +19757,16 @@
         <v>83</v>
       </c>
       <c r="K142" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="L142" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="L142" t="s" s="2">
+      <c r="M142" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="N142" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19821,7 +19816,7 @@
         <v>83</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -19839,27 +19834,27 @@
         <v>83</v>
       </c>
       <c r="AL142" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AM142" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="AM142" t="s" s="2">
+      <c r="AN142" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="AN142" t="s" s="2">
+      <c r="AO142" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP142" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="AO142" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP142" t="s" s="2">
-        <v>578</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19882,19 +19877,19 @@
         <v>83</v>
       </c>
       <c r="K143" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L143" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="L143" t="s" s="2">
+      <c r="M143" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="N143" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="M143" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="N143" t="s" s="2">
+      <c r="O143" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>83</v>
@@ -19943,7 +19938,7 @@
         <v>83</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -19955,19 +19950,19 @@
         <v>83</v>
       </c>
       <c r="AJ143" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AK143" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL143" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM143" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="AK143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL143" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM143" t="s" s="2">
+      <c r="AN143" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>83</v>
@@ -19978,10 +19973,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20096,10 +20091,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20216,14 +20211,14 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -20245,10 +20240,10 @@
         <v>139</v>
       </c>
       <c r="L146" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M146" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="M146" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>171</v>
@@ -20303,7 +20298,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -20338,10 +20333,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20364,13 +20359,13 @@
         <v>83</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="L147" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="M147" t="s" s="2">
         <v>596</v>
-      </c>
-      <c r="M147" t="s" s="2">
-        <v>597</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -20421,7 +20416,7 @@
         <v>83</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -20430,7 +20425,7 @@
         <v>94</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>106</v>
@@ -20442,10 +20437,10 @@
         <v>83</v>
       </c>
       <c r="AM147" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AN147" t="s" s="2">
         <v>599</v>
-      </c>
-      <c r="AN147" t="s" s="2">
-        <v>600</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>83</v>
@@ -20456,10 +20451,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20482,13 +20477,13 @@
         <v>83</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="L148" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M148" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="M148" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -20539,7 +20534,7 @@
         <v>83</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
@@ -20548,7 +20543,7 @@
         <v>94</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>106</v>
@@ -20560,10 +20555,10 @@
         <v>83</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>83</v>
@@ -20574,10 +20569,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20603,16 +20598,16 @@
         <v>211</v>
       </c>
       <c r="L149" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="M149" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="M149" t="s" s="2">
+      <c r="N149" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>83</v>
@@ -20640,11 +20635,11 @@
         <v>118</v>
       </c>
       <c r="Y149" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="Z149" t="s" s="2">
         <v>610</v>
       </c>
-      <c r="Z149" t="s" s="2">
-        <v>611</v>
-      </c>
       <c r="AA149" t="s" s="2">
         <v>83</v>
       </c>
@@ -20661,7 +20656,7 @@
         <v>83</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -20679,10 +20674,10 @@
         <v>83</v>
       </c>
       <c r="AL149" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AM149" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="AM149" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>433</v>
@@ -20696,10 +20691,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20725,16 +20720,16 @@
         <v>211</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>616</v>
       </c>
-      <c r="N150" t="s" s="2">
+      <c r="O150" t="s" s="2">
         <v>617</v>
-      </c>
-      <c r="O150" t="s" s="2">
-        <v>618</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>83</v>
@@ -20762,11 +20757,11 @@
         <v>346</v>
       </c>
       <c r="Y150" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="Z150" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="Z150" t="s" s="2">
-        <v>620</v>
-      </c>
       <c r="AA150" t="s" s="2">
         <v>83</v>
       </c>
@@ -20783,7 +20778,7 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -20801,10 +20796,10 @@
         <v>83</v>
       </c>
       <c r="AL150" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AM150" t="s" s="2">
         <v>612</v>
-      </c>
-      <c r="AM150" t="s" s="2">
-        <v>613</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>433</v>
@@ -20818,10 +20813,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20844,17 +20839,17 @@
         <v>83</v>
       </c>
       <c r="K151" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="L151" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="L151" t="s" s="2">
+      <c r="M151" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>83</v>
@@ -20903,7 +20898,7 @@
         <v>83</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -20927,7 +20922,7 @@
         <v>83</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>83</v>
@@ -20938,10 +20933,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20967,10 +20962,10 @@
         <v>228</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="M152" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21021,7 +21016,7 @@
         <v>83</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -21042,10 +21037,10 @@
         <v>83</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>83</v>
@@ -21056,10 +21051,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21082,16 +21077,16 @@
         <v>95</v>
       </c>
       <c r="K153" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="L153" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="L153" t="s" s="2">
+      <c r="M153" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N153" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="M153" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -21141,7 +21136,7 @@
         <v>83</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
@@ -21162,10 +21157,10 @@
         <v>83</v>
       </c>
       <c r="AM153" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AN153" t="s" s="2">
         <v>635</v>
-      </c>
-      <c r="AN153" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>83</v>
@@ -21176,10 +21171,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21202,16 +21197,16 @@
         <v>95</v>
       </c>
       <c r="K154" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="L154" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="L154" t="s" s="2">
+      <c r="M154" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="N154" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="M154" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -21261,7 +21256,7 @@
         <v>83</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -21282,10 +21277,10 @@
         <v>83</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>83</v>
@@ -21296,10 +21291,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21322,19 +21317,19 @@
         <v>95</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="L155" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="N155" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="M155" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="N155" t="s" s="2">
+      <c r="O155" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="O155" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>83</v>
@@ -21383,7 +21378,7 @@
         <v>83</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21404,10 +21399,10 @@
         <v>83</v>
       </c>
       <c r="AM155" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AN155" t="s" s="2">
         <v>646</v>
-      </c>
-      <c r="AN155" t="s" s="2">
-        <v>647</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>83</v>
@@ -21418,10 +21413,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21536,10 +21531,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21656,14 +21651,14 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -21685,10 +21680,10 @@
         <v>139</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="N158" t="s" s="2">
         <v>171</v>
@@ -21743,7 +21738,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -21778,10 +21773,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21807,13 +21802,13 @@
         <v>211</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="N159" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>654</v>
       </c>
       <c r="O159" t="s" s="2">
         <v>344</v>
@@ -21845,7 +21840,7 @@
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>83</v>
@@ -21863,7 +21858,7 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>94</v>
@@ -21881,7 +21876,7 @@
         <v>83</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>351</v>
@@ -21898,10 +21893,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21927,13 +21922,13 @@
         <v>406</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="M160" t="s" s="2">
+      <c r="N160" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>660</v>
       </c>
       <c r="O160" t="s" s="2">
         <v>409</v>
@@ -21985,7 +21980,7 @@
         <v>83</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -22003,7 +21998,7 @@
         <v>83</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>412</v>
@@ -22020,10 +22015,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22049,13 +22044,13 @@
         <v>211</v>
       </c>
       <c r="L161" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M161" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M161" t="s" s="2">
+      <c r="N161" t="s" s="2">
         <v>664</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>665</v>
       </c>
       <c r="O161" t="s" s="2">
         <v>418</v>
@@ -22107,7 +22102,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
@@ -22142,10 +22137,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22171,16 +22166,16 @@
         <v>211</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="M162" t="s" s="2">
+      <c r="N162" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="N162" t="s" s="2">
+      <c r="O162" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="O162" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>83</v>
@@ -22227,7 +22222,7 @@
         <v>143</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -22262,10 +22257,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>436</v>
@@ -22293,16 +22288,16 @@
         <v>211</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="M163" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N163" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N163" t="s" s="2">
-        <v>673</v>
-      </c>
       <c r="O163" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>83</v>
@@ -22351,7 +22346,7 @@
         <v>83</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -22386,10 +22381,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="B164" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22504,10 +22499,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="B165" t="s" s="2">
         <v>676</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22624,10 +22619,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="B166" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="B166" t="s" s="2">
-        <v>679</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22746,10 +22741,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="B167" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22864,10 +22859,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="B168" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22984,10 +22979,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="B169" t="s" s="2">
         <v>684</v>
-      </c>
-      <c r="B169" t="s" s="2">
-        <v>685</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23106,10 +23101,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="B170" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="B170" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23226,10 +23221,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="B171" t="s" s="2">
         <v>688</v>
-      </c>
-      <c r="B171" t="s" s="2">
-        <v>689</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23346,10 +23341,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="B172" t="s" s="2">
         <v>690</v>
-      </c>
-      <c r="B172" t="s" s="2">
-        <v>691</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23466,10 +23461,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B173" t="s" s="2">
         <v>692</v>
-      </c>
-      <c r="B173" t="s" s="2">
-        <v>693</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23588,10 +23583,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="B174" t="s" s="2">
         <v>694</v>
-      </c>
-      <c r="B174" t="s" s="2">
-        <v>695</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23710,10 +23705,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C175" t="s" s="2">
         <v>465</v>
@@ -23741,16 +23736,16 @@
         <v>211</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="M175" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N175" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N175" t="s" s="2">
-        <v>673</v>
-      </c>
       <c r="O175" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>83</v>
@@ -23799,7 +23794,7 @@
         <v>83</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -23834,10 +23829,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23952,10 +23947,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24072,10 +24067,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24194,10 +24189,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24312,10 +24307,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24432,10 +24427,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24554,10 +24549,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24674,10 +24669,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24794,10 +24789,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24914,10 +24909,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25036,10 +25031,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25158,10 +25153,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C187" t="s" s="2">
         <v>480</v>
@@ -25189,16 +25184,16 @@
         <v>211</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="M187" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N187" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N187" t="s" s="2">
-        <v>673</v>
-      </c>
       <c r="O187" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>83</v>
@@ -25247,7 +25242,7 @@
         <v>83</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -25282,10 +25277,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25400,10 +25395,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25520,10 +25515,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25642,10 +25637,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25760,10 +25755,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25880,10 +25875,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -26002,10 +25997,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26122,10 +26117,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26242,10 +26237,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26362,10 +26357,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26484,10 +26479,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26606,10 +26601,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C199" t="s" s="2">
         <v>495</v>
@@ -26637,16 +26632,16 @@
         <v>211</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="M199" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N199" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N199" t="s" s="2">
-        <v>673</v>
-      </c>
       <c r="O199" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>83</v>
@@ -26695,7 +26690,7 @@
         <v>83</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
@@ -26730,10 +26725,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26848,10 +26843,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26968,10 +26963,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27090,10 +27085,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27208,10 +27203,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27328,10 +27323,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27450,10 +27445,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27570,10 +27565,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27690,10 +27685,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27810,10 +27805,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27932,10 +27927,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28054,10 +28049,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C211" t="s" s="2">
         <v>510</v>
@@ -28085,16 +28080,16 @@
         <v>211</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="M211" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N211" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N211" t="s" s="2">
-        <v>673</v>
-      </c>
       <c r="O211" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>83</v>
@@ -28143,7 +28138,7 @@
         <v>83</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>81</v>
@@ -28178,10 +28173,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28296,10 +28291,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28416,10 +28411,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28538,10 +28533,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28656,10 +28651,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28776,10 +28771,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28898,10 +28893,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29018,10 +29013,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29138,10 +29133,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29258,10 +29253,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29380,10 +29375,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29502,10 +29497,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C223" t="s" s="2">
         <v>525</v>
@@ -29533,16 +29528,16 @@
         <v>211</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="M223" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="N223" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="N223" t="s" s="2">
-        <v>673</v>
-      </c>
       <c r="O223" t="s" s="2">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>83</v>
@@ -29591,7 +29586,7 @@
         <v>83</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -29626,10 +29621,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29744,10 +29739,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29864,10 +29859,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -29986,10 +29981,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30104,10 +30099,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30224,10 +30219,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30346,10 +30341,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30466,10 +30461,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30586,10 +30581,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30706,10 +30701,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30828,10 +30823,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30950,10 +30945,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30979,16 +30974,16 @@
         <v>84</v>
       </c>
       <c r="L235" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="M235" t="s" s="2">
         <v>757</v>
       </c>
-      <c r="M235" t="s" s="2">
+      <c r="N235" t="s" s="2">
         <v>758</v>
       </c>
-      <c r="N235" t="s" s="2">
+      <c r="O235" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="O235" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="P235" t="s" s="2">
         <v>83</v>
@@ -31037,7 +31032,7 @@
         <v>83</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>81</v>
@@ -31058,10 +31053,10 @@
         <v>83</v>
       </c>
       <c r="AM235" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AN235" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="AN235" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="AO235" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -1325,7 +1325,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1824,7 +1824,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -2083,7 +2083,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -2700,7 +2700,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="105.8828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="80.703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -1895,7 +1895,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>適用されるターゲット参照母集団のどの部分を示すコード。たとえば、通常または治療範囲。 / Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -2676,15 +2676,15 @@
   <dimension ref="A1:AP235"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="75.43359375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="55.65625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="20.203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="64.671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="47.71484375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2695,28 +2695,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="111.37890625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="80.703125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.48828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="69.1875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9041" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9042" uniqueCount="761">
   <si>
     <t>Property</t>
   </si>
@@ -1718,7 +1718,10 @@
 If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -19434,9 +19437,11 @@
       <c r="X139" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="Y139" s="2"/>
+      <c r="Y139" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="Z139" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>83</v>
@@ -19472,27 +19477,27 @@
         <v>83</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AN139" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO139" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19518,16 +19523,16 @@
         <v>211</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>83</v>
@@ -19555,10 +19560,10 @@
         <v>346</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>83</v>
@@ -19576,7 +19581,7 @@
         <v>83</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -19597,10 +19602,10 @@
         <v>83</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN140" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO140" t="s" s="2">
         <v>83</v>
@@ -19611,10 +19616,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19637,16 +19642,16 @@
         <v>83</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -19696,7 +19701,7 @@
         <v>83</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -19714,27 +19719,27 @@
         <v>83</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19757,16 +19762,16 @@
         <v>83</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -19816,7 +19821,7 @@
         <v>83</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -19834,27 +19839,27 @@
         <v>83</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP142" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19877,19 +19882,19 @@
         <v>83</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>83</v>
@@ -19938,7 +19943,7 @@
         <v>83</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -19950,7 +19955,7 @@
         <v>83</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>83</v>
@@ -19959,10 +19964,10 @@
         <v>83</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>83</v>
@@ -19973,10 +19978,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20091,10 +20096,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -20211,14 +20216,14 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
@@ -20240,10 +20245,10 @@
         <v>139</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>171</v>
@@ -20298,7 +20303,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -20333,10 +20338,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20359,13 +20364,13 @@
         <v>83</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -20416,7 +20421,7 @@
         <v>83</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -20425,7 +20430,7 @@
         <v>94</v>
       </c>
       <c r="AI147" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AJ147" t="s" s="2">
         <v>106</v>
@@ -20437,10 +20442,10 @@
         <v>83</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AO147" t="s" s="2">
         <v>83</v>
@@ -20451,10 +20456,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20477,13 +20482,13 @@
         <v>83</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -20534,7 +20539,7 @@
         <v>83</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
@@ -20543,7 +20548,7 @@
         <v>94</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>106</v>
@@ -20555,10 +20560,10 @@
         <v>83</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AN148" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AO148" t="s" s="2">
         <v>83</v>
@@ -20569,10 +20574,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -20598,16 +20603,16 @@
         <v>211</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>83</v>
@@ -20635,10 +20640,10 @@
         <v>118</v>
       </c>
       <c r="Y149" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="Z149" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>83</v>
@@ -20656,7 +20661,7 @@
         <v>83</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -20674,10 +20679,10 @@
         <v>83</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>433</v>
@@ -20691,10 +20696,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20720,16 +20725,16 @@
         <v>211</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>83</v>
@@ -20757,10 +20762,10 @@
         <v>346</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>83</v>
@@ -20778,7 +20783,7 @@
         <v>83</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -20796,10 +20801,10 @@
         <v>83</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>433</v>
@@ -20813,10 +20818,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20839,17 +20844,17 @@
         <v>83</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>83</v>
@@ -20898,7 +20903,7 @@
         <v>83</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -20922,7 +20927,7 @@
         <v>83</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>83</v>
@@ -20933,10 +20938,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -20962,10 +20967,10 @@
         <v>228</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -21016,7 +21021,7 @@
         <v>83</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -21037,10 +21042,10 @@
         <v>83</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AO152" t="s" s="2">
         <v>83</v>
@@ -21051,10 +21056,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -21077,16 +21082,16 @@
         <v>95</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -21136,7 +21141,7 @@
         <v>83</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
@@ -21157,10 +21162,10 @@
         <v>83</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>83</v>
@@ -21171,10 +21176,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -21197,16 +21202,16 @@
         <v>95</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -21256,7 +21261,7 @@
         <v>83</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -21277,10 +21282,10 @@
         <v>83</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>83</v>
@@ -21291,10 +21296,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21317,19 +21322,19 @@
         <v>95</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>83</v>
@@ -21378,7 +21383,7 @@
         <v>83</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21399,10 +21404,10 @@
         <v>83</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>83</v>
@@ -21413,10 +21418,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21531,10 +21536,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21651,14 +21656,14 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
@@ -21680,10 +21685,10 @@
         <v>139</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N158" t="s" s="2">
         <v>171</v>
@@ -21738,7 +21743,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -21773,10 +21778,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -21802,13 +21807,13 @@
         <v>211</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O159" t="s" s="2">
         <v>344</v>
@@ -21840,7 +21845,7 @@
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>83</v>
@@ -21858,7 +21863,7 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>94</v>
@@ -21876,7 +21881,7 @@
         <v>83</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AM159" t="s" s="2">
         <v>351</v>
@@ -21893,10 +21898,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21922,13 +21927,13 @@
         <v>406</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="O160" t="s" s="2">
         <v>409</v>
@@ -21980,7 +21985,7 @@
         <v>83</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -21998,7 +22003,7 @@
         <v>83</v>
       </c>
       <c r="AL160" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AM160" t="s" s="2">
         <v>412</v>
@@ -22015,10 +22020,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -22044,13 +22049,13 @@
         <v>211</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="O161" t="s" s="2">
         <v>418</v>
@@ -22102,7 +22107,7 @@
         <v>83</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
@@ -22137,10 +22142,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -22166,16 +22171,16 @@
         <v>211</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>83</v>
@@ -22222,7 +22227,7 @@
         <v>143</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -22257,10 +22262,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C163" t="s" s="2">
         <v>436</v>
@@ -22288,16 +22293,16 @@
         <v>211</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>83</v>
@@ -22346,7 +22351,7 @@
         <v>83</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -22381,10 +22386,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22499,10 +22504,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22619,10 +22624,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22741,10 +22746,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22859,10 +22864,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22979,10 +22984,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -23101,10 +23106,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -23221,10 +23226,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -23341,10 +23346,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -23461,10 +23466,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23583,10 +23588,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23705,10 +23710,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C175" t="s" s="2">
         <v>465</v>
@@ -23736,16 +23741,16 @@
         <v>211</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>83</v>
@@ -23794,7 +23799,7 @@
         <v>83</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -23829,10 +23834,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23947,10 +23952,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24067,10 +24072,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -24189,10 +24194,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -24307,10 +24312,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24427,10 +24432,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24549,10 +24554,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -24669,10 +24674,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24789,10 +24794,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24909,10 +24914,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -25031,10 +25036,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -25153,10 +25158,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C187" t="s" s="2">
         <v>480</v>
@@ -25184,16 +25189,16 @@
         <v>211</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>83</v>
@@ -25242,7 +25247,7 @@
         <v>83</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -25277,10 +25282,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -25395,10 +25400,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -25515,10 +25520,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25637,10 +25642,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25755,10 +25760,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25875,10 +25880,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25997,10 +26002,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -26117,10 +26122,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -26237,10 +26242,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -26357,10 +26362,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -26479,10 +26484,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26601,10 +26606,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C199" t="s" s="2">
         <v>495</v>
@@ -26632,16 +26637,16 @@
         <v>211</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P199" t="s" s="2">
         <v>83</v>
@@ -26690,7 +26695,7 @@
         <v>83</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>81</v>
@@ -26725,10 +26730,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -26843,10 +26848,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26963,10 +26968,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -27085,10 +27090,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -27203,10 +27208,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -27323,10 +27328,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -27445,10 +27450,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -27565,10 +27570,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27685,10 +27690,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27805,10 +27810,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27927,10 +27932,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28049,10 +28054,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C211" t="s" s="2">
         <v>510</v>
@@ -28080,16 +28085,16 @@
         <v>211</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O211" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P211" t="s" s="2">
         <v>83</v>
@@ -28138,7 +28143,7 @@
         <v>83</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>81</v>
@@ -28173,10 +28178,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -28291,10 +28296,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -28411,10 +28416,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -28533,10 +28538,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28651,10 +28656,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28771,10 +28776,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28893,10 +28898,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -29013,10 +29018,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -29133,10 +29138,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -29253,10 +29258,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -29375,10 +29380,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -29497,10 +29502,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C223" t="s" s="2">
         <v>525</v>
@@ -29528,16 +29533,16 @@
         <v>211</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="O223" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="P223" t="s" s="2">
         <v>83</v>
@@ -29586,7 +29591,7 @@
         <v>83</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>81</v>
@@ -29621,10 +29626,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -29739,10 +29744,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -29859,10 +29864,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -29981,10 +29986,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -30099,10 +30104,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -30219,10 +30224,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -30341,10 +30346,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -30461,10 +30466,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -30581,10 +30586,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -30701,10 +30706,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -30823,10 +30828,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -30945,10 +30950,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -30974,16 +30979,16 @@
         <v>84</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="O235" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P235" t="s" s="2">
         <v>83</v>
@@ -31032,7 +31037,7 @@
         <v>83</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>81</v>
@@ -31053,10 +31058,10 @@
         <v>83</v>
       </c>
       <c r="AM235" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN235" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AO235" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -692,7 +692,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1099,7 +1099,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1151,7 +1151,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1328,7 +1328,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1357,7 +1357,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1721,7 +1721,7 @@
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1751,7 +1751,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1788,7 +1788,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1863,7 +1863,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1913,7 +1913,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1946,7 +1946,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -695,7 +695,7 @@
     <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:coding.system}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>94</v>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>94</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>94</v>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>94</v>
@@ -12745,7 +12745,7 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G84" t="s" s="2">
         <v>94</v>
@@ -14193,7 +14193,7 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>94</v>
@@ -15641,7 +15641,7 @@
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>94</v>
@@ -17089,7 +17089,7 @@
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G120" t="s" s="2">
         <v>94</v>
@@ -18537,7 +18537,7 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>94</v>
@@ -22995,7 +22995,7 @@
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G169" t="s" s="2">
         <v>94</v>
@@ -24443,7 +24443,7 @@
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G181" t="s" s="2">
         <v>94</v>
@@ -25891,7 +25891,7 @@
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G193" t="s" s="2">
         <v>94</v>
@@ -27339,7 +27339,7 @@
       </c>
       <c r="E205" s="2"/>
       <c r="F205" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G205" t="s" s="2">
         <v>94</v>
@@ -28787,7 +28787,7 @@
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G217" t="s" s="2">
         <v>94</v>
@@ -30235,7 +30235,7 @@
       </c>
       <c r="E229" s="2"/>
       <c r="F229" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G229" t="s" s="2">
         <v>94</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -720,6 +720,14 @@
     <t>必要なカテゴリバリューセットに加えて、この要素は、所有者のカテゴリの定義に基づいてさまざまな分類スキームを許可し、効果的に複数のカテゴリを一度に使用できます。粒度のレベルは、値セットのカテゴリの概念によって定義されます。 / In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS"/&gt;
+    &lt;code value="procedure"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
   </si>
   <si>
@@ -873,9 +881,6 @@
   </si>
   <si>
     <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>procedure</t>
   </si>
   <si>
     <t>Coding.code</t>
@@ -989,42 +994,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Observation.category:second.id</t>
-  </si>
-  <si>
-    <t>Observation.category:second.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding.code</t>
-  </si>
-  <si>
-    <t>11524-6</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.category:second.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.category:second.text</t>
-  </si>
-  <si>
     <t>Observation.category:third</t>
   </si>
   <si>
@@ -1042,6 +1011,42 @@
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationElectrocardiogramExtraCategory_VS</t>
+  </si>
+  <si>
+    <t>Observation.category:third.id</t>
+  </si>
+  <si>
+    <t>Observation.category:third.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:third.coding</t>
+  </si>
+  <si>
+    <t>Observation.category:third.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category:third.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:third.coding.system</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_ObservationElectrocardiogramExtraCategory_CS</t>
+  </si>
+  <si>
+    <t>Observation.category:third.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.category:third.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.category:third.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.category:third.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.category:third.text</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -5060,7 +5065,7 @@
         <v>83</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>83</v>
+        <v>225</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>83</v>
@@ -5079,7 +5084,7 @@
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>83</v>
@@ -5132,10 +5137,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5158,13 +5163,13 @@
         <v>83</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -5215,7 +5220,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -5239,7 +5244,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -5250,10 +5255,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5279,10 +5284,10 @@
         <v>139</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>171</v>
@@ -5326,7 +5331,7 @@
         <v>142</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>83</v>
@@ -5335,7 +5340,7 @@
         <v>143</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5359,7 +5364,7 @@
         <v>83</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>83</v>
@@ -5370,10 +5375,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5396,19 +5401,19 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -5457,7 +5462,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5478,10 +5483,10 @@
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5492,10 +5497,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5518,13 +5523,13 @@
         <v>83</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -5575,7 +5580,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5599,7 +5604,7 @@
         <v>83</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -5610,10 +5615,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5639,10 +5644,10 @@
         <v>139</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>171</v>
@@ -5686,7 +5691,7 @@
         <v>142</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>83</v>
@@ -5695,7 +5700,7 @@
         <v>143</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5719,7 +5724,7 @@
         <v>83</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
@@ -5730,10 +5735,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5759,23 +5764,23 @@
         <v>108</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>83</v>
@@ -5817,7 +5822,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5838,10 +5843,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5852,10 +5857,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5878,16 +5883,16 @@
         <v>95</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5937,7 +5942,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5958,10 +5963,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5972,10 +5977,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6001,14 +6006,14 @@
         <v>114</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>83</v>
@@ -6018,7 +6023,7 @@
         <v>83</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>276</v>
+        <v>83</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>83</v>
@@ -6118,7 +6123,7 @@
         <v>95</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>282</v>
@@ -6360,7 +6365,7 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>300</v>
@@ -6583,9 +6588,11 @@
         <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="C33" s="2"/>
+        <v>210</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="D33" t="s" s="2">
         <v>83</v>
       </c>
@@ -6606,16 +6613,20 @@
         <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>229</v>
+        <v>309</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
@@ -6624,7 +6635,7 @@
         <v>83</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>83</v>
+        <v>315</v>
       </c>
       <c r="T33" t="s" s="2">
         <v>83</v>
@@ -6639,13 +6650,11 @@
         <v>83</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>83</v>
+        <v>316</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>83</v>
@@ -6663,19 +6672,19 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -6687,10 +6696,10 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>83</v>
+        <v>219</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>83</v>
@@ -6698,21 +6707,21 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>83</v>
@@ -6724,17 +6733,15 @@
         <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>139</v>
+        <v>229</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>83</v>
@@ -6771,31 +6778,31 @@
         <v>83</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>237</v>
+        <v>83</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>83</v>
@@ -6807,7 +6814,7 @@
         <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6818,14 +6825,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6841,23 +6848,21 @@
         <v>83</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>241</v>
+        <v>139</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6893,19 +6898,19 @@
         <v>83</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>83</v>
+        <v>238</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6917,7 +6922,7 @@
         <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>83</v>
@@ -6926,10 +6931,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>247</v>
+        <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6940,10 +6945,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6954,7 +6959,7 @@
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>83</v>
@@ -6963,19 +6968,23 @@
         <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
@@ -7023,19 +7032,19 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>83</v>
@@ -7044,10 +7053,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>83</v>
+        <v>248</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -7058,21 +7067,21 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>168</v>
+        <v>83</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>83</v>
@@ -7084,17 +7093,15 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>139</v>
+        <v>229</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -7131,31 +7138,31 @@
         <v>83</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>237</v>
+        <v>83</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>143</v>
+        <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>83</v>
@@ -7167,7 +7174,7 @@
         <v>83</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -7178,21 +7185,21 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>83</v>
+        <v>168</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>83</v>
@@ -7201,23 +7208,21 @@
         <v>83</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>83</v>
       </c>
@@ -7253,31 +7258,31 @@
         <v>83</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>83</v>
+        <v>238</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>83</v>
@@ -7286,10 +7291,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>261</v>
+        <v>83</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -7300,10 +7305,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7326,18 +7331,20 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>228</v>
+        <v>108</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="O39" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
       </c>
@@ -7346,7 +7353,7 @@
         <v>83</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>83</v>
+        <v>323</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>83</v>
@@ -7385,7 +7392,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7406,10 +7413,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -7420,10 +7427,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7446,18 +7453,18 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>114</v>
+        <v>229</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>267</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -7466,7 +7473,7 @@
         <v>83</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>320</v>
+        <v>83</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>83</v>
@@ -7505,7 +7512,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7526,10 +7533,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -7540,10 +7547,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7566,17 +7573,17 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>228</v>
+        <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -7625,7 +7632,7 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -7646,10 +7653,10 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>83</v>
@@ -7660,10 +7667,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7686,19 +7693,17 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>290</v>
+        <v>229</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7747,7 +7752,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7768,10 +7773,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7782,10 +7787,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7808,19 +7813,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>228</v>
+        <v>290</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7869,7 +7874,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7890,10 +7895,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7904,14 +7909,12 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7929,22 +7932,22 @@
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>326</v>
+        <v>302</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>214</v>
+        <v>303</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
@@ -7954,7 +7957,7 @@
         <v>83</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>327</v>
+        <v>83</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>83</v>
@@ -7969,11 +7972,13 @@
         <v>83</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="Z44" t="s" s="2">
-        <v>328</v>
+        <v>83</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>83</v>
@@ -7991,13 +7996,13 @@
         <v>83</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>210</v>
+        <v>304</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
@@ -8012,13 +8017,13 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>218</v>
+        <v>306</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>219</v>
+        <v>83</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>83</v>
@@ -9390,13 +9395,13 @@
         <v>83</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9447,7 +9452,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9471,7 +9476,7 @@
         <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>83</v>
@@ -9511,10 +9516,10 @@
         <v>139</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>171</v>
@@ -9558,7 +9563,7 @@
         <v>142</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>83</v>
@@ -9567,7 +9572,7 @@
         <v>143</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9591,7 +9596,7 @@
         <v>83</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>83</v>
@@ -9628,19 +9633,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9689,7 +9694,7 @@
         <v>83</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9710,10 +9715,10 @@
         <v>83</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
@@ -9750,13 +9755,13 @@
         <v>83</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9807,7 +9812,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9831,7 +9836,7 @@
         <v>83</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
@@ -9871,10 +9876,10 @@
         <v>139</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>171</v>
@@ -9918,7 +9923,7 @@
         <v>142</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>83</v>
@@ -9927,7 +9932,7 @@
         <v>143</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9951,7 +9956,7 @@
         <v>83</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
@@ -9997,10 +10002,10 @@
         <v>442</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -10049,7 +10054,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10070,10 +10075,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -10110,16 +10115,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10169,7 +10174,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -10190,10 +10195,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -10233,14 +10238,14 @@
         <v>114</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -10350,7 +10355,7 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>282</v>
@@ -10592,7 +10597,7 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L66" t="s" s="2">
         <v>300</v>
@@ -10838,13 +10843,13 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10895,7 +10900,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10919,7 +10924,7 @@
         <v>83</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10959,10 +10964,10 @@
         <v>139</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>171</v>
@@ -11006,7 +11011,7 @@
         <v>142</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>83</v>
@@ -11015,7 +11020,7 @@
         <v>143</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -11039,7 +11044,7 @@
         <v>83</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -11076,19 +11081,19 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>83</v>
@@ -11137,7 +11142,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11158,10 +11163,10 @@
         <v>83</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
@@ -11198,13 +11203,13 @@
         <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11255,7 +11260,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11279,7 +11284,7 @@
         <v>83</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11319,10 +11324,10 @@
         <v>139</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>171</v>
@@ -11366,7 +11371,7 @@
         <v>142</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>83</v>
@@ -11375,7 +11380,7 @@
         <v>143</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11399,7 +11404,7 @@
         <v>83</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
@@ -11445,10 +11450,10 @@
         <v>462</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>83</v>
@@ -11497,7 +11502,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11518,10 +11523,10 @@
         <v>83</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
@@ -11558,16 +11563,16 @@
         <v>95</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11617,7 +11622,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11638,10 +11643,10 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11681,14 +11686,14 @@
         <v>114</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>83</v>
@@ -11798,7 +11803,7 @@
         <v>95</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>282</v>
@@ -12040,7 +12045,7 @@
         <v>95</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L78" t="s" s="2">
         <v>300</v>
@@ -12286,13 +12291,13 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12343,7 +12348,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12367,7 +12372,7 @@
         <v>83</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12407,10 +12412,10 @@
         <v>139</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>171</v>
@@ -12454,7 +12459,7 @@
         <v>142</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>83</v>
@@ -12463,7 +12468,7 @@
         <v>143</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12487,7 +12492,7 @@
         <v>83</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12524,19 +12529,19 @@
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12585,7 +12590,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12606,10 +12611,10 @@
         <v>83</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12646,13 +12651,13 @@
         <v>83</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12703,7 +12708,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12727,7 +12732,7 @@
         <v>83</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12767,10 +12772,10 @@
         <v>139</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N84" t="s" s="2">
         <v>171</v>
@@ -12814,7 +12819,7 @@
         <v>142</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>83</v>
@@ -12823,7 +12828,7 @@
         <v>143</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12847,7 +12852,7 @@
         <v>83</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12893,10 +12898,10 @@
         <v>477</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>83</v>
@@ -12945,7 +12950,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12966,10 +12971,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -13006,16 +13011,16 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -13065,7 +13070,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13086,10 +13091,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -13129,14 +13134,14 @@
         <v>114</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>83</v>
@@ -13246,7 +13251,7 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>282</v>
@@ -13488,7 +13493,7 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>300</v>
@@ -13734,13 +13739,13 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13791,7 +13796,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13815,7 +13820,7 @@
         <v>83</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13855,10 +13860,10 @@
         <v>139</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>171</v>
@@ -13902,7 +13907,7 @@
         <v>142</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>83</v>
@@ -13911,7 +13916,7 @@
         <v>143</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13935,7 +13940,7 @@
         <v>83</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
@@ -13972,19 +13977,19 @@
         <v>95</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -14033,7 +14038,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14054,10 +14059,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -14094,13 +14099,13 @@
         <v>83</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14151,7 +14156,7 @@
         <v>83</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14175,7 +14180,7 @@
         <v>83</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>83</v>
@@ -14215,10 +14220,10 @@
         <v>139</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>171</v>
@@ -14262,7 +14267,7 @@
         <v>142</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>83</v>
@@ -14271,7 +14276,7 @@
         <v>143</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -14295,7 +14300,7 @@
         <v>83</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>83</v>
@@ -14341,10 +14346,10 @@
         <v>492</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>83</v>
@@ -14393,7 +14398,7 @@
         <v>83</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -14414,10 +14419,10 @@
         <v>83</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>83</v>
@@ -14454,16 +14459,16 @@
         <v>95</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14513,7 +14518,7 @@
         <v>83</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -14534,10 +14539,10 @@
         <v>83</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>83</v>
@@ -14577,14 +14582,14 @@
         <v>114</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>83</v>
@@ -14694,7 +14699,7 @@
         <v>95</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L100" t="s" s="2">
         <v>282</v>
@@ -14936,7 +14941,7 @@
         <v>95</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L102" t="s" s="2">
         <v>300</v>
@@ -15182,13 +15187,13 @@
         <v>83</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15239,7 +15244,7 @@
         <v>83</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -15263,7 +15268,7 @@
         <v>83</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>83</v>
@@ -15303,10 +15308,10 @@
         <v>139</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N105" t="s" s="2">
         <v>171</v>
@@ -15350,7 +15355,7 @@
         <v>142</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>83</v>
@@ -15359,7 +15364,7 @@
         <v>143</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -15383,7 +15388,7 @@
         <v>83</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>83</v>
@@ -15420,19 +15425,19 @@
         <v>95</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>83</v>
@@ -15481,7 +15486,7 @@
         <v>83</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -15502,10 +15507,10 @@
         <v>83</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>83</v>
@@ -15542,13 +15547,13 @@
         <v>83</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15599,7 +15604,7 @@
         <v>83</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -15623,7 +15628,7 @@
         <v>83</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>83</v>
@@ -15663,10 +15668,10 @@
         <v>139</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>171</v>
@@ -15710,7 +15715,7 @@
         <v>142</v>
       </c>
       <c r="AC108" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD108" t="s" s="2">
         <v>83</v>
@@ -15719,7 +15724,7 @@
         <v>143</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -15743,7 +15748,7 @@
         <v>83</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>83</v>
@@ -15789,10 +15794,10 @@
         <v>507</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>83</v>
@@ -15841,7 +15846,7 @@
         <v>83</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -15862,10 +15867,10 @@
         <v>83</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>83</v>
@@ -15902,16 +15907,16 @@
         <v>95</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15961,7 +15966,7 @@
         <v>83</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -15982,10 +15987,10 @@
         <v>83</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>83</v>
@@ -16025,14 +16030,14 @@
         <v>114</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>83</v>
@@ -16142,7 +16147,7 @@
         <v>95</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L112" t="s" s="2">
         <v>282</v>
@@ -16384,7 +16389,7 @@
         <v>95</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L114" t="s" s="2">
         <v>300</v>
@@ -16630,13 +16635,13 @@
         <v>83</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16687,7 +16692,7 @@
         <v>83</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -16711,7 +16716,7 @@
         <v>83</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>83</v>
@@ -16751,10 +16756,10 @@
         <v>139</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>171</v>
@@ -16798,7 +16803,7 @@
         <v>142</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>83</v>
@@ -16807,7 +16812,7 @@
         <v>143</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -16831,7 +16836,7 @@
         <v>83</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>83</v>
@@ -16868,19 +16873,19 @@
         <v>95</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>83</v>
@@ -16929,7 +16934,7 @@
         <v>83</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -16950,10 +16955,10 @@
         <v>83</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>83</v>
@@ -16990,13 +16995,13 @@
         <v>83</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -17047,7 +17052,7 @@
         <v>83</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -17071,7 +17076,7 @@
         <v>83</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>83</v>
@@ -17111,10 +17116,10 @@
         <v>139</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N120" t="s" s="2">
         <v>171</v>
@@ -17158,7 +17163,7 @@
         <v>142</v>
       </c>
       <c r="AC120" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD120" t="s" s="2">
         <v>83</v>
@@ -17167,7 +17172,7 @@
         <v>143</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -17191,7 +17196,7 @@
         <v>83</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>83</v>
@@ -17237,10 +17242,10 @@
         <v>522</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>83</v>
@@ -17289,7 +17294,7 @@
         <v>83</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -17310,10 +17315,10 @@
         <v>83</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>83</v>
@@ -17350,16 +17355,16 @@
         <v>95</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -17409,7 +17414,7 @@
         <v>83</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -17430,10 +17435,10 @@
         <v>83</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO122" t="s" s="2">
         <v>83</v>
@@ -17473,14 +17478,14 @@
         <v>114</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>83</v>
@@ -17590,7 +17595,7 @@
         <v>95</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L124" t="s" s="2">
         <v>282</v>
@@ -17832,7 +17837,7 @@
         <v>95</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L126" t="s" s="2">
         <v>300</v>
@@ -18680,13 +18685,13 @@
         <v>83</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -18737,7 +18742,7 @@
         <v>83</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -18761,7 +18766,7 @@
         <v>83</v>
       </c>
       <c r="AN133" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO133" t="s" s="2">
         <v>83</v>
@@ -18801,10 +18806,10 @@
         <v>139</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N134" t="s" s="2">
         <v>171</v>
@@ -18857,7 +18862,7 @@
         <v>83</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -18881,7 +18886,7 @@
         <v>83</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>83</v>
@@ -19640,7 +19645,7 @@
         <v>83</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L141" t="s" s="2">
         <v>617</v>
@@ -20120,13 +20125,13 @@
         <v>83</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -20177,7 +20182,7 @@
         <v>83</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -20201,7 +20206,7 @@
         <v>83</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>83</v>
@@ -20241,10 +20246,10 @@
         <v>139</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N146" t="s" s="2">
         <v>171</v>
@@ -20297,7 +20302,7 @@
         <v>83</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -20321,7 +20326,7 @@
         <v>83</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>83</v>
@@ -21088,13 +21093,13 @@
         <v>83</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -21145,7 +21150,7 @@
         <v>83</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
@@ -21169,7 +21174,7 @@
         <v>83</v>
       </c>
       <c r="AN153" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO153" t="s" s="2">
         <v>83</v>
@@ -21209,10 +21214,10 @@
         <v>139</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N154" t="s" s="2">
         <v>171</v>
@@ -21256,7 +21261,7 @@
         <v>142</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>83</v>
@@ -21265,7 +21270,7 @@
         <v>143</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -21289,7 +21294,7 @@
         <v>83</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO154" t="s" s="2">
         <v>83</v>
@@ -21326,19 +21331,19 @@
         <v>95</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>83</v>
@@ -21387,7 +21392,7 @@
         <v>83</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -21408,10 +21413,10 @@
         <v>83</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>83</v>
@@ -21448,13 +21453,13 @@
         <v>83</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21505,7 +21510,7 @@
         <v>83</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -21529,7 +21534,7 @@
         <v>83</v>
       </c>
       <c r="AN156" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO156" t="s" s="2">
         <v>83</v>
@@ -21569,10 +21574,10 @@
         <v>139</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N157" t="s" s="2">
         <v>171</v>
@@ -21616,7 +21621,7 @@
         <v>142</v>
       </c>
       <c r="AC157" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD157" t="s" s="2">
         <v>83</v>
@@ -21625,7 +21630,7 @@
         <v>143</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -21649,7 +21654,7 @@
         <v>83</v>
       </c>
       <c r="AN157" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO157" t="s" s="2">
         <v>83</v>
@@ -21695,10 +21700,10 @@
         <v>442</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>83</v>
@@ -21747,7 +21752,7 @@
         <v>83</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -21768,10 +21773,10 @@
         <v>83</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>83</v>
@@ -21808,16 +21813,16 @@
         <v>95</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -21867,7 +21872,7 @@
         <v>83</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -21888,10 +21893,10 @@
         <v>83</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>83</v>
@@ -21931,14 +21936,14 @@
         <v>114</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>83</v>
@@ -22048,7 +22053,7 @@
         <v>95</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L161" t="s" s="2">
         <v>282</v>
@@ -22290,7 +22295,7 @@
         <v>95</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L163" t="s" s="2">
         <v>300</v>
@@ -22536,13 +22541,13 @@
         <v>83</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -22593,7 +22598,7 @@
         <v>83</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -22617,7 +22622,7 @@
         <v>83</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>83</v>
@@ -22657,10 +22662,10 @@
         <v>139</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N166" t="s" s="2">
         <v>171</v>
@@ -22704,7 +22709,7 @@
         <v>142</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>83</v>
@@ -22713,7 +22718,7 @@
         <v>143</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -22737,7 +22742,7 @@
         <v>83</v>
       </c>
       <c r="AN166" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO166" t="s" s="2">
         <v>83</v>
@@ -22774,19 +22779,19 @@
         <v>95</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>83</v>
@@ -22835,7 +22840,7 @@
         <v>83</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -22856,10 +22861,10 @@
         <v>83</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>83</v>
@@ -22896,13 +22901,13 @@
         <v>83</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -22953,7 +22958,7 @@
         <v>83</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -22977,7 +22982,7 @@
         <v>83</v>
       </c>
       <c r="AN168" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO168" t="s" s="2">
         <v>83</v>
@@ -23017,10 +23022,10 @@
         <v>139</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N169" t="s" s="2">
         <v>171</v>
@@ -23064,7 +23069,7 @@
         <v>142</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>83</v>
@@ -23073,7 +23078,7 @@
         <v>143</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
@@ -23097,7 +23102,7 @@
         <v>83</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO169" t="s" s="2">
         <v>83</v>
@@ -23143,10 +23148,10 @@
         <v>462</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>83</v>
@@ -23195,7 +23200,7 @@
         <v>83</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -23216,10 +23221,10 @@
         <v>83</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>83</v>
@@ -23256,16 +23261,16 @@
         <v>95</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -23315,7 +23320,7 @@
         <v>83</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
@@ -23336,10 +23341,10 @@
         <v>83</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>83</v>
@@ -23379,14 +23384,14 @@
         <v>114</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>83</v>
@@ -23496,7 +23501,7 @@
         <v>95</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L173" t="s" s="2">
         <v>282</v>
@@ -23738,7 +23743,7 @@
         <v>95</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L175" t="s" s="2">
         <v>300</v>
@@ -23984,13 +23989,13 @@
         <v>83</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -24041,7 +24046,7 @@
         <v>83</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
@@ -24065,7 +24070,7 @@
         <v>83</v>
       </c>
       <c r="AN177" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO177" t="s" s="2">
         <v>83</v>
@@ -24105,10 +24110,10 @@
         <v>139</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N178" t="s" s="2">
         <v>171</v>
@@ -24152,7 +24157,7 @@
         <v>142</v>
       </c>
       <c r="AC178" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD178" t="s" s="2">
         <v>83</v>
@@ -24161,7 +24166,7 @@
         <v>143</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
@@ -24185,7 +24190,7 @@
         <v>83</v>
       </c>
       <c r="AN178" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO178" t="s" s="2">
         <v>83</v>
@@ -24222,19 +24227,19 @@
         <v>95</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>83</v>
@@ -24283,7 +24288,7 @@
         <v>83</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -24304,10 +24309,10 @@
         <v>83</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO179" t="s" s="2">
         <v>83</v>
@@ -24344,13 +24349,13 @@
         <v>83</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
@@ -24401,7 +24406,7 @@
         <v>83</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
@@ -24425,7 +24430,7 @@
         <v>83</v>
       </c>
       <c r="AN180" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO180" t="s" s="2">
         <v>83</v>
@@ -24465,10 +24470,10 @@
         <v>139</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N181" t="s" s="2">
         <v>171</v>
@@ -24512,7 +24517,7 @@
         <v>142</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>83</v>
@@ -24521,7 +24526,7 @@
         <v>143</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -24545,7 +24550,7 @@
         <v>83</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>83</v>
@@ -24591,10 +24596,10 @@
         <v>477</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>83</v>
@@ -24643,7 +24648,7 @@
         <v>83</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -24664,10 +24669,10 @@
         <v>83</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN182" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO182" t="s" s="2">
         <v>83</v>
@@ -24704,16 +24709,16 @@
         <v>95</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
@@ -24763,7 +24768,7 @@
         <v>83</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -24784,10 +24789,10 @@
         <v>83</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO183" t="s" s="2">
         <v>83</v>
@@ -24827,14 +24832,14 @@
         <v>114</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N184" s="2"/>
       <c r="O184" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>83</v>
@@ -24944,7 +24949,7 @@
         <v>95</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L185" t="s" s="2">
         <v>282</v>
@@ -25186,7 +25191,7 @@
         <v>95</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L187" t="s" s="2">
         <v>300</v>
@@ -25432,13 +25437,13 @@
         <v>83</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N189" s="2"/>
       <c r="O189" s="2"/>
@@ -25489,7 +25494,7 @@
         <v>83</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>81</v>
@@ -25513,7 +25518,7 @@
         <v>83</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>83</v>
@@ -25553,10 +25558,10 @@
         <v>139</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N190" t="s" s="2">
         <v>171</v>
@@ -25600,7 +25605,7 @@
         <v>142</v>
       </c>
       <c r="AC190" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD190" t="s" s="2">
         <v>83</v>
@@ -25609,7 +25614,7 @@
         <v>143</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>81</v>
@@ -25633,7 +25638,7 @@
         <v>83</v>
       </c>
       <c r="AN190" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO190" t="s" s="2">
         <v>83</v>
@@ -25670,19 +25675,19 @@
         <v>95</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>83</v>
@@ -25731,7 +25736,7 @@
         <v>83</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
@@ -25752,10 +25757,10 @@
         <v>83</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO191" t="s" s="2">
         <v>83</v>
@@ -25792,13 +25797,13 @@
         <v>83</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -25849,7 +25854,7 @@
         <v>83</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>81</v>
@@ -25873,7 +25878,7 @@
         <v>83</v>
       </c>
       <c r="AN192" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO192" t="s" s="2">
         <v>83</v>
@@ -25913,10 +25918,10 @@
         <v>139</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N193" t="s" s="2">
         <v>171</v>
@@ -25960,7 +25965,7 @@
         <v>142</v>
       </c>
       <c r="AC193" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD193" t="s" s="2">
         <v>83</v>
@@ -25969,7 +25974,7 @@
         <v>143</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>81</v>
@@ -25993,7 +25998,7 @@
         <v>83</v>
       </c>
       <c r="AN193" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO193" t="s" s="2">
         <v>83</v>
@@ -26039,10 +26044,10 @@
         <v>492</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P194" t="s" s="2">
         <v>83</v>
@@ -26091,7 +26096,7 @@
         <v>83</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>81</v>
@@ -26112,10 +26117,10 @@
         <v>83</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO194" t="s" s="2">
         <v>83</v>
@@ -26152,16 +26157,16 @@
         <v>95</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -26211,7 +26216,7 @@
         <v>83</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>81</v>
@@ -26232,10 +26237,10 @@
         <v>83</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO195" t="s" s="2">
         <v>83</v>
@@ -26275,14 +26280,14 @@
         <v>114</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>83</v>
@@ -26392,7 +26397,7 @@
         <v>95</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L197" t="s" s="2">
         <v>282</v>
@@ -26634,7 +26639,7 @@
         <v>95</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L199" t="s" s="2">
         <v>300</v>
@@ -26880,13 +26885,13 @@
         <v>83</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
@@ -26937,7 +26942,7 @@
         <v>83</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
@@ -26961,7 +26966,7 @@
         <v>83</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>83</v>
@@ -27001,10 +27006,10 @@
         <v>139</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N202" t="s" s="2">
         <v>171</v>
@@ -27048,7 +27053,7 @@
         <v>142</v>
       </c>
       <c r="AC202" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD202" t="s" s="2">
         <v>83</v>
@@ -27057,7 +27062,7 @@
         <v>143</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
@@ -27081,7 +27086,7 @@
         <v>83</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO202" t="s" s="2">
         <v>83</v>
@@ -27118,19 +27123,19 @@
         <v>95</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O203" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P203" t="s" s="2">
         <v>83</v>
@@ -27179,7 +27184,7 @@
         <v>83</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
@@ -27200,10 +27205,10 @@
         <v>83</v>
       </c>
       <c r="AM203" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN203" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO203" t="s" s="2">
         <v>83</v>
@@ -27240,13 +27245,13 @@
         <v>83</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -27297,7 +27302,7 @@
         <v>83</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -27321,7 +27326,7 @@
         <v>83</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO204" t="s" s="2">
         <v>83</v>
@@ -27361,10 +27366,10 @@
         <v>139</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N205" t="s" s="2">
         <v>171</v>
@@ -27408,7 +27413,7 @@
         <v>142</v>
       </c>
       <c r="AC205" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD205" t="s" s="2">
         <v>83</v>
@@ -27417,7 +27422,7 @@
         <v>143</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>81</v>
@@ -27441,7 +27446,7 @@
         <v>83</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO205" t="s" s="2">
         <v>83</v>
@@ -27487,10 +27492,10 @@
         <v>507</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O206" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P206" t="s" s="2">
         <v>83</v>
@@ -27539,7 +27544,7 @@
         <v>83</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>81</v>
@@ -27560,10 +27565,10 @@
         <v>83</v>
       </c>
       <c r="AM206" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>83</v>
@@ -27600,16 +27605,16 @@
         <v>95</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
@@ -27659,7 +27664,7 @@
         <v>83</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
@@ -27680,10 +27685,10 @@
         <v>83</v>
       </c>
       <c r="AM207" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>83</v>
@@ -27723,14 +27728,14 @@
         <v>114</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N208" s="2"/>
       <c r="O208" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P208" t="s" s="2">
         <v>83</v>
@@ -27840,7 +27845,7 @@
         <v>95</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L209" t="s" s="2">
         <v>282</v>
@@ -28082,7 +28087,7 @@
         <v>95</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L211" t="s" s="2">
         <v>300</v>
@@ -28328,13 +28333,13 @@
         <v>83</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" s="2"/>
@@ -28385,7 +28390,7 @@
         <v>83</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
@@ -28409,7 +28414,7 @@
         <v>83</v>
       </c>
       <c r="AN213" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO213" t="s" s="2">
         <v>83</v>
@@ -28449,10 +28454,10 @@
         <v>139</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N214" t="s" s="2">
         <v>171</v>
@@ -28496,7 +28501,7 @@
         <v>142</v>
       </c>
       <c r="AC214" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD214" t="s" s="2">
         <v>83</v>
@@ -28505,7 +28510,7 @@
         <v>143</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>81</v>
@@ -28529,7 +28534,7 @@
         <v>83</v>
       </c>
       <c r="AN214" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO214" t="s" s="2">
         <v>83</v>
@@ -28566,19 +28571,19 @@
         <v>95</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O215" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>83</v>
@@ -28627,7 +28632,7 @@
         <v>83</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>81</v>
@@ -28648,10 +28653,10 @@
         <v>83</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>83</v>
@@ -28688,13 +28693,13 @@
         <v>83</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N216" s="2"/>
       <c r="O216" s="2"/>
@@ -28745,7 +28750,7 @@
         <v>83</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>81</v>
@@ -28769,7 +28774,7 @@
         <v>83</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>83</v>
@@ -28809,10 +28814,10 @@
         <v>139</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="N217" t="s" s="2">
         <v>171</v>
@@ -28856,7 +28861,7 @@
         <v>142</v>
       </c>
       <c r="AC217" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AD217" t="s" s="2">
         <v>83</v>
@@ -28865,7 +28870,7 @@
         <v>143</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>81</v>
@@ -28889,7 +28894,7 @@
         <v>83</v>
       </c>
       <c r="AN217" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AO217" t="s" s="2">
         <v>83</v>
@@ -28935,10 +28940,10 @@
         <v>522</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O218" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P218" t="s" s="2">
         <v>83</v>
@@ -28987,7 +28992,7 @@
         <v>83</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>81</v>
@@ -29008,10 +29013,10 @@
         <v>83</v>
       </c>
       <c r="AM218" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AN218" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AO218" t="s" s="2">
         <v>83</v>
@@ -29048,16 +29053,16 @@
         <v>95</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="O219" s="2"/>
       <c r="P219" t="s" s="2">
@@ -29107,7 +29112,7 @@
         <v>83</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>81</v>
@@ -29128,10 +29133,10 @@
         <v>83</v>
       </c>
       <c r="AM219" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AN219" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AO219" t="s" s="2">
         <v>83</v>
@@ -29171,14 +29176,14 @@
         <v>114</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N220" s="2"/>
       <c r="O220" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P220" t="s" s="2">
         <v>83</v>
@@ -29288,7 +29293,7 @@
         <v>95</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L221" t="s" s="2">
         <v>282</v>
@@ -29530,7 +29535,7 @@
         <v>95</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L223" t="s" s="2">
         <v>300</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -1111,7 +1111,7 @@
     <t>このObservationの対象となる患者や患者群、機器、場所に関する情報</t>
   </si>
   <si>
-    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明なデバイスによって観察が行われるケースである。この場合、観察は何らかのコンテキスト/チャネルマッチング技術を介して患者にマッチングされる必要があり、患者にマッチングされれば、その時点で本要素を更新する必要がある。</t>
+    <t>この要素は1..1のcardinalityになるはずと考えられる。この要素が欠損値になる唯一の状況は、対象患者が不明な機器によって観察が行われるケースである。この場合、観察は何らかのコンテキスト・チャネル照合技術を介して患者に照合される必要があり、患者に照合されれば、その時点で本要素を更新する必要がある。</t>
   </si>
   <si>
     <t>あなたが彼らが誰または何をしているのかわからない場合、観察には価値がありません。 / Observations have no value if you don't know who or what they're about.</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-observation-electrocardiogram.xlsx
@@ -618,7 +618,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
